--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="FSC" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="FSM" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="EE" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="FSE" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">EE!$A$1:$L$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">FSE!$A$1:$L$18</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">FSM!$A$1:$N$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -616,7 +616,7 @@
   </si>
   <si>
     <t xml:space="preserve">SS2041 Critical Thinking
-BFT-4A,B,C,D
+BS(FT)-4A,B,C,D
 2024</t>
   </si>
   <si>
@@ -696,9 +696,9 @@
   </si>
   <si>
     <t xml:space="preserve">SS2006 Macro Economics
-BAF-4A,B,C
+BS(AF)-4A,B,C
 BBA-4A,B,C
-BSBA-4A,B,C
+BS(BA)-4A,B,C
 2024</t>
   </si>
   <si>
@@ -749,12 +749,12 @@
   </si>
   <si>
     <t xml:space="preserve">BA2006 Fundamentals of Business Analytics
-B(BA)-4A,B,C
+BS(BA)-4A,B,C
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">SS2019 Psychology
-BAF-2A,B
+BS(AF)-2A,B
 2025</t>
   </si>
   <si>
@@ -789,7 +789,7 @@
   <si>
     <t xml:space="preserve">SS2008 Business Communication–I
 BBA-8A
-BSBA-8A
+BS(BA)-8A
 2022</t>
   </si>
   <si>
@@ -799,7 +799,7 @@
   </si>
   <si>
     <t xml:space="preserve">AF2001 Corporate Accounting – I
-B(AF)-4A
+BS(AF)-4A
 2024</t>
   </si>
   <si>
@@ -842,7 +842,7 @@
   </si>
   <si>
     <t xml:space="preserve">MG3033-Principles of Leadership
-BAF-8A
+BS(AF)-8A
 2022</t>
   </si>
   <si>
@@ -852,7 +852,7 @@
   </si>
   <si>
     <t xml:space="preserve">AF2002 Corporate Accounting – II
-B(AF)-4A,B,C
+BS(AF)-4A,B,C
 2024</t>
   </si>
   <si>
@@ -876,7 +876,7 @@
   </si>
   <si>
     <t xml:space="preserve">MG4002 Communication for Managers
-BFT-8A
+BS(FT)-8A
 2022</t>
   </si>
   <si>
@@ -902,7 +902,7 @@
   </si>
   <si>
     <t xml:space="preserve">SS1013 Ideology and Constitution of Pakistan
-BFT-4A,B,C,D
+BS(FT)-4A,B,C,D
 2024</t>
   </si>
   <si>
@@ -935,7 +935,7 @@
   </si>
   <si>
     <t xml:space="preserve">AF4013 Artificial Intelligence in Business Decision
-BFT-8A, 8B
+BS(FT)-8A, 8B
 2022</t>
   </si>
   <si>
@@ -945,7 +945,7 @@
   </si>
   <si>
     <t xml:space="preserve">SS1015 Pakistan Studies
-B(AF)-4A,B,C
+BS(AF)-4A,B,C
 BBA-4A,B,C
 BS(BA)-4A,B,C
 2024</t>
@@ -1003,18 +1003,18 @@
   </si>
   <si>
     <t xml:space="preserve">CS2018 Operating Systems
-BEE-6A,B
+BS(EE)-6A,B
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">EE1005 Digital Logic Design
-BCE-4A
-BEE-4A,B
+BS(CE)-4A
+BS(EE)-4A,B
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">EE3003 Analogue and Digital Communication
-BEE-6A
+BS(EE)-6A
 2023</t>
   </si>
   <si>
@@ -1022,7 +1022,7 @@
   </si>
   <si>
     <t xml:space="preserve">CS2002 Data Structures and Algorithms
-BCE-4A
+BS(CE)-4A
 2024</t>
   </si>
   <si>
@@ -1032,17 +1032,17 @@
   </si>
   <si>
     <t xml:space="preserve">EE4033 Industrial Processes Control 
-BEE-8A
+BS(EE)-8A
 2022</t>
   </si>
   <si>
     <t xml:space="preserve">ME2001 Basic Mechanical Engineering
-BEE-6A
+BS(EE)-6A
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">CS1002 Programming Fundamentals
-BEE-4A
+BS(EE)-4A
 2024</t>
   </si>
   <si>
@@ -1052,7 +1052,7 @@
   </si>
   <si>
     <t xml:space="preserve">EE3031 Digital Signal Processing 
-BEE-6A
+BS(EE)-6A
 2023</t>
   </si>
   <si>
@@ -1063,12 +1063,12 @@
   </si>
   <si>
     <t xml:space="preserve">EE4031 Computer Architecture
-BEE-6A,B
+BS(EE)-6A,B
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">EE2011 Probability and Random Processes
-BEE-4A,B,C
+BS(EE)-4A,B,C
 2024</t>
   </si>
   <si>
@@ -1078,22 +1078,22 @@
   </si>
   <si>
     <t xml:space="preserve">EE3032 Power Electronics
-BEE-6A
+BS(EE)-6A
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">MT2005 Probability and Statistics
-BCE-4A
+BS(CE)-4A
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">IO3031 Introduction to Internet of Things
-BEE-8A
+BS(EE)-8A
 2022</t>
   </si>
   <si>
     <t xml:space="preserve">MG3008 Engineering Economics
-BEE-6A,B
+BS(EE)-6A,B
 2023</t>
   </si>
   <si>
@@ -1104,12 +1104,12 @@
   </si>
   <si>
     <t xml:space="preserve">CS2021 Object Oriented Data Structures
-BEE-4A
+BS(EE)-4A
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">SS2010 Communication Skills
-BEE-6A,B
+BS(EE)-6A,B
 2023</t>
   </si>
   <si>
@@ -1119,19 +1119,19 @@
   </si>
   <si>
     <t xml:space="preserve">SS2011  Technical Communication Skills
-BCE-4A
-BEE-4A,B
+BS(CE)-4A
+BS(EE)-4A,B
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">MG4011 Entrepreneurship
-BEE-8A
-BEE-8B
+BS(EE)-8A
+BS(EE)-8B
 2022</t>
   </si>
   <si>
     <t xml:space="preserve">EE3004 Feedback Control System
-BEE-6A,B
+BS(EE)-6A,B
 2023</t>
   </si>
   <si>
@@ -1141,43 +1141,43 @@
   </si>
   <si>
     <t xml:space="preserve">EE3034 VLSI
-BEE-8A
+BS(EE)-8A
 2022</t>
   </si>
   <si>
     <t xml:space="preserve">EE2004 Electrical Network Analysis
-BEE-4A,B
+BS(EE)-4A,B
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">EE2015 Electro-Mechanical Systems
-BEE-4A,B
+BS(EE)-4A,B
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">EE4043 Network Programming
-BEE-8A
+BS(EE)-8A
 2022</t>
   </si>
   <si>
     <t xml:space="preserve">EE2010 Electro-Mechanical Systems
-BEE-6A,B
+BS(EE)-6A,B
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">EE2008 Signals and Systems 
-BCE-4A
-BEE-4A,B
+BS(CE)-4A
+BS(EE)-4A,B
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">MT1009 Linear Algebra and Diff. Equations
-BEE-4A
+BS(EE)-4A
 2024</t>
   </si>
   <si>
     <t xml:space="preserve">NS1007 Applied Physics
-BEE-2A
+BS(EE)-2A
 2025</t>
   </si>
 </sst>
@@ -1191,7 +1191,7 @@
     <numFmt numFmtId="166" formatCode="h:mm\ AM/PM"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="35">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1332,11 +1332,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="18"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1390,12 +1385,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="16"/>
@@ -1719,892 +1708,884 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="220">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5455,7 +5436,7 @@
     </row>
     <row r="19" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="128"/>
-      <c r="B19" s="131" t="s">
+      <c r="B19" s="94" t="s">
         <v>153</v>
       </c>
       <c r="C19" s="92"/>
@@ -5480,12 +5461,12 @@
       <c r="N19" s="119"/>
       <c r="P19" s="123"/>
     </row>
-    <row r="20" s="133" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" s="132" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="128"/>
       <c r="B20" s="85" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="132"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="81" t="s">
         <v>159</v>
       </c>
@@ -5503,52 +5484,52 @@
       </c>
       <c r="M20" s="98"/>
       <c r="N20" s="100"/>
-      <c r="P20" s="134"/>
-    </row>
-    <row r="21" s="133" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P20" s="133"/>
+    </row>
+    <row r="21" s="132" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="128"/>
-      <c r="C21" s="132"/>
+      <c r="C21" s="131"/>
       <c r="D21" s="81"/>
       <c r="E21" s="118"/>
       <c r="F21" s="18"/>
       <c r="G21" s="118"/>
       <c r="I21" s="95"/>
-      <c r="J21" s="135"/>
+      <c r="J21" s="134"/>
       <c r="K21" s="118"/>
       <c r="M21" s="98"/>
       <c r="N21" s="100"/>
-      <c r="P21" s="134"/>
-    </row>
-    <row r="22" s="133" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P21" s="133"/>
+    </row>
+    <row r="22" s="132" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="128"/>
-      <c r="C22" s="132"/>
+      <c r="C22" s="131"/>
       <c r="E22" s="118"/>
       <c r="F22" s="18"/>
       <c r="G22" s="118"/>
       <c r="I22" s="95"/>
-      <c r="J22" s="135"/>
+      <c r="J22" s="134"/>
       <c r="K22" s="118"/>
       <c r="M22" s="98"/>
       <c r="N22" s="100"/>
-      <c r="P22" s="134"/>
+      <c r="P22" s="133"/>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="136"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="137"/>
-      <c r="I23" s="137"/>
-      <c r="J23" s="137"/>
-      <c r="K23" s="137"/>
-      <c r="L23" s="137"/>
-      <c r="M23" s="137"/>
-      <c r="N23" s="138"/>
+      <c r="A23" s="135"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="136"/>
+      <c r="F23" s="136"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="136"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="137"/>
       <c r="O23" s="90"/>
-      <c r="P23" s="139"/>
+      <c r="P23" s="138"/>
     </row>
     <row r="24" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="80" t="n">
@@ -5569,7 +5550,7 @@
       <c r="H24" s="88" t="s">
         <v>165</v>
       </c>
-      <c r="I24" s="140"/>
+      <c r="I24" s="139"/>
       <c r="J24" s="81" t="s">
         <v>166</v>
       </c>
@@ -5589,7 +5570,7 @@
       <c r="B25" s="120" t="s">
         <v>169</v>
       </c>
-      <c r="C25" s="141"/>
+      <c r="C25" s="140"/>
       <c r="D25" s="119"/>
       <c r="E25" s="124"/>
       <c r="F25" s="88" t="s">
@@ -5618,7 +5599,7 @@
       <c r="B26" s="85" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="141"/>
+      <c r="C26" s="140"/>
       <c r="D26" s="100"/>
       <c r="E26" s="124"/>
       <c r="F26" s="88"/>
@@ -5636,19 +5617,19 @@
       </c>
       <c r="P26" s="101"/>
     </row>
-    <row r="27" s="133" customFormat="true" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" s="132" customFormat="true" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="80"/>
       <c r="B27" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="141"/>
+      <c r="C27" s="140"/>
       <c r="D27" s="100"/>
       <c r="E27" s="124"/>
-      <c r="F27" s="142"/>
+      <c r="F27" s="141"/>
       <c r="G27" s="124"/>
-      <c r="H27" s="143"/>
+      <c r="H27" s="142"/>
       <c r="I27" s="124"/>
-      <c r="J27" s="144" t="s">
+      <c r="J27" s="143" t="s">
         <v>179</v>
       </c>
       <c r="K27" s="124"/>
@@ -5657,74 +5638,74 @@
       </c>
       <c r="M27" s="124"/>
       <c r="N27" s="101"/>
-      <c r="P27" s="134"/>
-    </row>
-    <row r="28" s="133" customFormat="true" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P27" s="133"/>
+    </row>
+    <row r="28" s="132" customFormat="true" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="80"/>
       <c r="B28" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="141"/>
+      <c r="C28" s="140"/>
       <c r="D28" s="108"/>
       <c r="E28" s="124"/>
       <c r="F28" s="110"/>
       <c r="G28" s="124"/>
-      <c r="H28" s="145"/>
+      <c r="H28" s="144"/>
       <c r="I28" s="124"/>
       <c r="J28" s="103"/>
       <c r="K28" s="124"/>
-      <c r="L28" s="146"/>
+      <c r="L28" s="145"/>
       <c r="M28" s="124"/>
-      <c r="N28" s="147"/>
-      <c r="O28" s="146"/>
-      <c r="P28" s="147"/>
+      <c r="N28" s="146"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="146"/>
     </row>
     <row r="29" s="26" customFormat="true" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="147" t="s">
         <v>102</v>
       </c>
-      <c r="B29" s="148"/>
-      <c r="C29" s="148"/>
-      <c r="D29" s="148"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
-      <c r="G29" s="148"/>
-      <c r="H29" s="148"/>
-      <c r="I29" s="148"/>
-      <c r="J29" s="148"/>
-      <c r="K29" s="148"/>
-      <c r="L29" s="148"/>
-      <c r="M29" s="148"/>
-      <c r="N29" s="148"/>
+      <c r="B29" s="147"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="147"/>
+      <c r="F29" s="147"/>
+      <c r="G29" s="147"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="147"/>
+      <c r="N29" s="147"/>
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="149"/>
-      <c r="B30" s="149"/>
-      <c r="C30" s="149"/>
-      <c r="D30" s="149"/>
-      <c r="E30" s="149"/>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="149"/>
-      <c r="I30" s="149"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="149"/>
-      <c r="N30" s="149"/>
+      <c r="A30" s="148"/>
+      <c r="B30" s="148"/>
+      <c r="C30" s="148"/>
+      <c r="D30" s="148"/>
+      <c r="E30" s="148"/>
+      <c r="F30" s="148"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="148"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="148"/>
+      <c r="L30" s="148"/>
+      <c r="M30" s="148"/>
+      <c r="N30" s="148"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="150"/>
-      <c r="B31" s="151"/>
-      <c r="C31" s="149"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="149"/>
-      <c r="F31" s="149"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="149"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="149"/>
+      <c r="A31" s="149"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="148"/>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="148"/>
+      <c r="I31" s="148"/>
+      <c r="J31" s="148"/>
+      <c r="K31" s="148"/>
       <c r="L31" s="71"/>
       <c r="M31" s="71"/>
       <c r="N31" s="71" t="s">
@@ -5732,34 +5713,34 @@
       </c>
     </row>
     <row r="32" s="75" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="152"/>
-      <c r="B32" s="151"/>
-      <c r="C32" s="153"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="155" t="s">
+      <c r="A32" s="151"/>
+      <c r="B32" s="150"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="154" t="s">
         <v>182</v>
       </c>
-      <c r="I32" s="155"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="156"/>
+      <c r="I32" s="154"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="154"/>
+      <c r="L32" s="155"/>
       <c r="M32" s="71"/>
-      <c r="N32" s="156" t="s">
+      <c r="N32" s="155" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G33" s="154"/>
+      <c r="G33" s="153"/>
       <c r="H33" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I33" s="155"/>
-      <c r="K33" s="155"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="155"/>
+      <c r="I33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
     </row>
     <row r="35" s="75" customFormat="true" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="73"/>
@@ -5841,56 +5822,56 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="156" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
     </row>
     <row r="2" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
     </row>
     <row r="3" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="159" t="s">
+      <c r="A3" s="158" t="s">
         <v>183</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="160"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="159"/>
       <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="161" customFormat="true" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" s="160" customFormat="true" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
@@ -5922,401 +5903,401 @@
       <c r="A5" s="15" t="n">
         <v>46121</v>
       </c>
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="161" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164" t="s">
+      <c r="C5" s="162"/>
+      <c r="D5" s="163" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="165"/>
-      <c r="F5" s="166" t="s">
+      <c r="E5" s="164"/>
+      <c r="F5" s="165" t="s">
         <v>186</v>
       </c>
-      <c r="G5" s="167"/>
-      <c r="H5" s="168" t="s">
+      <c r="G5" s="166"/>
+      <c r="H5" s="167" t="s">
         <v>187</v>
       </c>
-      <c r="I5" s="169"/>
-      <c r="J5" s="170" t="s">
+      <c r="I5" s="168"/>
+      <c r="J5" s="169" t="s">
         <v>188</v>
       </c>
-      <c r="K5" s="171"/>
-      <c r="L5" s="172" t="s">
+      <c r="K5" s="170"/>
+      <c r="L5" s="171" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="6" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15"/>
-      <c r="B6" s="173" t="s">
+      <c r="B6" s="172" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="174"/>
-      <c r="D6" s="164"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="166"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="177"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="179"/>
-      <c r="L6" s="180" t="s">
+      <c r="C6" s="173"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="174"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="168"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="178"/>
+      <c r="L6" s="179" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="7" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15"/>
-      <c r="B7" s="173"/>
-      <c r="C7" s="181"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="166"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="177"/>
-      <c r="I7" s="177"/>
-      <c r="J7" s="183"/>
-      <c r="K7" s="179"/>
-      <c r="L7" s="184" t="s">
+      <c r="B7" s="172"/>
+      <c r="C7" s="180"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="174"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="175"/>
+      <c r="H7" s="176"/>
+      <c r="I7" s="176"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="183" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="8" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15"/>
-      <c r="B8" s="170" t="s">
+      <c r="B8" s="169" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="185"/>
-      <c r="D8" s="186"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="189"/>
-      <c r="H8" s="190"/>
-      <c r="I8" s="190"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="192"/>
-      <c r="L8" s="173"/>
+      <c r="C8" s="184"/>
+      <c r="D8" s="185"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="188"/>
+      <c r="H8" s="189"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="190"/>
+      <c r="K8" s="191"/>
+      <c r="L8" s="172"/>
     </row>
     <row r="9" s="73" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="193"/>
-      <c r="B9" s="194"/>
-      <c r="C9" s="194"/>
-      <c r="D9" s="194"/>
-      <c r="E9" s="194"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
-      <c r="H9" s="194"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="194"/>
-      <c r="K9" s="194"/>
-      <c r="L9" s="195"/>
+      <c r="A9" s="192"/>
+      <c r="B9" s="193"/>
+      <c r="C9" s="193"/>
+      <c r="D9" s="193"/>
+      <c r="E9" s="193"/>
+      <c r="F9" s="193"/>
+      <c r="G9" s="193"/>
+      <c r="H9" s="193"/>
+      <c r="I9" s="193"/>
+      <c r="J9" s="193"/>
+      <c r="K9" s="193"/>
+      <c r="L9" s="194"/>
     </row>
     <row r="10" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>46122</v>
       </c>
-      <c r="B10" s="196" t="s">
+      <c r="B10" s="161" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="197"/>
-      <c r="D10" s="198" t="s">
+      <c r="C10" s="195"/>
+      <c r="D10" s="196" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="165"/>
-      <c r="F10" s="173" t="s">
+      <c r="E10" s="164"/>
+      <c r="F10" s="172" t="s">
         <v>196</v>
       </c>
-      <c r="G10" s="165"/>
+      <c r="G10" s="164"/>
       <c r="H10" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="169"/>
-      <c r="J10" s="199" t="s">
+      <c r="I10" s="168"/>
+      <c r="J10" s="197" t="s">
         <v>197</v>
       </c>
-      <c r="K10" s="200"/>
-      <c r="L10" s="172" t="s">
+      <c r="K10" s="198"/>
+      <c r="L10" s="171" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="11" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15"/>
-      <c r="B11" s="196" t="s">
+      <c r="B11" s="161" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="201"/>
-      <c r="D11" s="198"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="175"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="196"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="174"/>
       <c r="H11" s="114"/>
-      <c r="I11" s="177"/>
-      <c r="J11" s="199" t="s">
+      <c r="I11" s="176"/>
+      <c r="J11" s="197" t="s">
         <v>200</v>
       </c>
-      <c r="K11" s="202"/>
-      <c r="L11" s="166" t="s">
+      <c r="K11" s="200"/>
+      <c r="L11" s="165" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="12" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15"/>
-      <c r="B12" s="180" t="s">
+      <c r="B12" s="179" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="201"/>
-      <c r="D12" s="169"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="178"/>
-      <c r="G12" s="175"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="168"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="177"/>
+      <c r="G12" s="174"/>
       <c r="H12" s="114"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="178"/>
-      <c r="K12" s="202"/>
-      <c r="L12" s="203"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="177"/>
+      <c r="K12" s="200"/>
+      <c r="L12" s="201"/>
     </row>
     <row r="13" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15"/>
-      <c r="B13" s="204"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="191"/>
-      <c r="G13" s="175"/>
+      <c r="B13" s="202"/>
+      <c r="C13" s="199"/>
+      <c r="D13" s="189"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="190"/>
+      <c r="G13" s="174"/>
       <c r="H13" s="114"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="191"/>
-      <c r="K13" s="205"/>
-      <c r="L13" s="203"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="190"/>
+      <c r="K13" s="203"/>
+      <c r="L13" s="201"/>
     </row>
     <row r="14" s="73" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="206"/>
-      <c r="B14" s="207"/>
-      <c r="C14" s="207"/>
-      <c r="D14" s="207"/>
-      <c r="E14" s="207"/>
-      <c r="F14" s="207"/>
-      <c r="G14" s="207"/>
-      <c r="H14" s="207"/>
-      <c r="I14" s="207"/>
-      <c r="J14" s="207"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="208"/>
+      <c r="A14" s="204"/>
+      <c r="B14" s="205"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
+      <c r="F14" s="205"/>
+      <c r="G14" s="205"/>
+      <c r="H14" s="205"/>
+      <c r="I14" s="205"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="206"/>
     </row>
     <row r="15" s="73" customFormat="true" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
         <v>46123</v>
       </c>
-      <c r="B15" s="209" t="s">
+      <c r="B15" s="207" t="s">
         <v>203</v>
       </c>
-      <c r="C15" s="210"/>
-      <c r="D15" s="173" t="s">
+      <c r="C15" s="208"/>
+      <c r="D15" s="172" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="165"/>
-      <c r="F15" s="211" t="s">
+      <c r="E15" s="164"/>
+      <c r="F15" s="209" t="s">
         <v>205</v>
       </c>
-      <c r="G15" s="167"/>
-      <c r="H15" s="199" t="s">
+      <c r="G15" s="166"/>
+      <c r="H15" s="197" t="s">
         <v>206</v>
       </c>
-      <c r="I15" s="169"/>
-      <c r="J15" s="170" t="s">
+      <c r="I15" s="168"/>
+      <c r="J15" s="169" t="s">
         <v>207</v>
       </c>
-      <c r="K15" s="169"/>
-      <c r="L15" s="172" t="s">
+      <c r="K15" s="168"/>
+      <c r="L15" s="171" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="16" s="73" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15"/>
-      <c r="B16" s="209"/>
-      <c r="C16" s="205"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="175"/>
-      <c r="F16" s="211"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="199"/>
-      <c r="I16" s="177"/>
-      <c r="K16" s="177"/>
-      <c r="L16" s="212" t="s">
+      <c r="B16" s="207"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="172"/>
+      <c r="E16" s="174"/>
+      <c r="F16" s="209"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="197"/>
+      <c r="I16" s="176"/>
+      <c r="K16" s="176"/>
+      <c r="L16" s="210" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="17" s="73" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15"/>
-      <c r="B17" s="169"/>
-      <c r="C17" s="205"/>
-      <c r="D17" s="178"/>
-      <c r="E17" s="175"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="176"/>
-      <c r="H17" s="178"/>
-      <c r="I17" s="177"/>
-      <c r="K17" s="177"/>
-      <c r="L17" s="203"/>
+      <c r="B17" s="168"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="174"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="175"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="176"/>
+      <c r="K17" s="176"/>
+      <c r="L17" s="201"/>
     </row>
     <row r="18" s="73" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15"/>
-      <c r="B18" s="190"/>
-      <c r="C18" s="213"/>
-      <c r="D18" s="191"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="190"/>
-      <c r="G18" s="176"/>
-      <c r="H18" s="191"/>
-      <c r="I18" s="177"/>
-      <c r="K18" s="177"/>
-      <c r="L18" s="203"/>
+      <c r="B18" s="189"/>
+      <c r="C18" s="211"/>
+      <c r="D18" s="190"/>
+      <c r="E18" s="174"/>
+      <c r="F18" s="189"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="190"/>
+      <c r="I18" s="176"/>
+      <c r="K18" s="176"/>
+      <c r="L18" s="201"/>
     </row>
     <row r="19" s="73" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="206"/>
-      <c r="B19" s="207"/>
-      <c r="C19" s="207"/>
-      <c r="D19" s="207"/>
-      <c r="E19" s="207"/>
-      <c r="F19" s="207"/>
-      <c r="G19" s="207"/>
-      <c r="H19" s="207"/>
-      <c r="I19" s="207"/>
-      <c r="J19" s="207"/>
-      <c r="K19" s="207"/>
-      <c r="L19" s="208"/>
+      <c r="A19" s="204"/>
+      <c r="B19" s="205"/>
+      <c r="C19" s="205"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="205"/>
+      <c r="G19" s="205"/>
+      <c r="H19" s="205"/>
+      <c r="I19" s="205"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="205"/>
+      <c r="L19" s="206"/>
     </row>
     <row r="20" s="73" customFormat="true" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
         <v>46125</v>
       </c>
-      <c r="B20" s="209" t="s">
+      <c r="B20" s="207" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="163"/>
-      <c r="D20" s="173" t="s">
+      <c r="C20" s="162"/>
+      <c r="D20" s="172" t="s">
         <v>211</v>
       </c>
-      <c r="E20" s="165"/>
-      <c r="F20" s="180" t="s">
+      <c r="E20" s="164"/>
+      <c r="F20" s="179" t="s">
         <v>212</v>
       </c>
-      <c r="G20" s="167"/>
-      <c r="H20" s="211" t="s">
+      <c r="G20" s="166"/>
+      <c r="H20" s="209" t="s">
         <v>213</v>
       </c>
-      <c r="I20" s="169"/>
-      <c r="J20" s="178"/>
-      <c r="K20" s="169"/>
-      <c r="L20" s="166" t="s">
+      <c r="I20" s="168"/>
+      <c r="J20" s="177"/>
+      <c r="K20" s="168"/>
+      <c r="L20" s="165" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="21" s="73" customFormat="true" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15"/>
-      <c r="B21" s="209"/>
-      <c r="C21" s="214"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="180" t="s">
+      <c r="B21" s="207"/>
+      <c r="C21" s="212"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="179" t="s">
         <v>215</v>
       </c>
-      <c r="G21" s="176"/>
-      <c r="H21" s="211"/>
-      <c r="I21" s="177"/>
-      <c r="J21" s="183"/>
-      <c r="K21" s="177"/>
-      <c r="L21" s="164" t="s">
+      <c r="G21" s="175"/>
+      <c r="H21" s="209"/>
+      <c r="I21" s="176"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="176"/>
+      <c r="L21" s="163" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="22" s="73" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15"/>
-      <c r="B22" s="166" t="s">
+      <c r="B22" s="165" t="s">
         <v>217</v>
       </c>
-      <c r="C22" s="163"/>
-      <c r="D22" s="215" t="s">
+      <c r="C22" s="162"/>
+      <c r="D22" s="213" t="s">
         <v>218</v>
       </c>
-      <c r="E22" s="175"/>
-      <c r="F22" s="216"/>
-      <c r="G22" s="176"/>
+      <c r="E22" s="174"/>
+      <c r="F22" s="214"/>
+      <c r="G22" s="175"/>
       <c r="H22" s="82"/>
-      <c r="I22" s="177"/>
-      <c r="J22" s="183"/>
-      <c r="K22" s="177"/>
-      <c r="L22" s="170" t="s">
+      <c r="I22" s="176"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="176"/>
+      <c r="L22" s="169" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="23" s="73" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15"/>
-      <c r="B23" s="217"/>
-      <c r="D23" s="190"/>
-      <c r="E23" s="187"/>
-      <c r="F23" s="204"/>
-      <c r="G23" s="189"/>
-      <c r="H23" s="204"/>
-      <c r="I23" s="190"/>
-      <c r="J23" s="218"/>
-      <c r="K23" s="190"/>
-      <c r="L23" s="191"/>
+      <c r="B23" s="215"/>
+      <c r="D23" s="189"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="202"/>
+      <c r="G23" s="188"/>
+      <c r="H23" s="202"/>
+      <c r="I23" s="189"/>
+      <c r="J23" s="216"/>
+      <c r="K23" s="189"/>
+      <c r="L23" s="190"/>
     </row>
     <row r="24" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="219" t="s">
+      <c r="A24" s="217" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="219"/>
-      <c r="C24" s="219"/>
-      <c r="D24" s="219"/>
-      <c r="E24" s="219"/>
-      <c r="F24" s="219"/>
-      <c r="G24" s="219"/>
-      <c r="H24" s="219"/>
-      <c r="I24" s="219"/>
-      <c r="J24" s="219"/>
-      <c r="K24" s="219"/>
-      <c r="L24" s="219"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="217"/>
+      <c r="D24" s="217"/>
+      <c r="E24" s="217"/>
+      <c r="F24" s="217"/>
+      <c r="G24" s="217"/>
+      <c r="H24" s="217"/>
+      <c r="I24" s="217"/>
+      <c r="J24" s="217"/>
+      <c r="K24" s="217"/>
+      <c r="L24" s="217"/>
     </row>
     <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="220"/>
-      <c r="B25" s="220"/>
-      <c r="C25" s="220"/>
-      <c r="D25" s="220"/>
-      <c r="E25" s="220"/>
-      <c r="G25" s="220"/>
-      <c r="H25" s="220"/>
-      <c r="I25" s="220"/>
-      <c r="J25" s="220"/>
-      <c r="K25" s="220"/>
-      <c r="L25" s="220"/>
+      <c r="A25" s="218"/>
+      <c r="B25" s="218"/>
+      <c r="C25" s="218"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
+      <c r="G25" s="218"/>
+      <c r="H25" s="218"/>
+      <c r="I25" s="218"/>
+      <c r="J25" s="218"/>
+      <c r="K25" s="218"/>
+      <c r="L25" s="218"/>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="220"/>
-      <c r="E26" s="220"/>
-      <c r="F26" s="220"/>
-      <c r="G26" s="220"/>
-      <c r="H26" s="220"/>
-      <c r="I26" s="220"/>
-      <c r="J26" s="220"/>
-      <c r="K26" s="220"/>
-      <c r="L26" s="220"/>
+      <c r="A26" s="218"/>
+      <c r="E26" s="218"/>
+      <c r="F26" s="218"/>
+      <c r="G26" s="218"/>
+      <c r="H26" s="218"/>
+      <c r="I26" s="218"/>
+      <c r="J26" s="218"/>
+      <c r="K26" s="218"/>
+      <c r="L26" s="218"/>
     </row>
     <row r="27" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="221"/>
-      <c r="E27" s="221"/>
-      <c r="G27" s="221"/>
-      <c r="I27" s="221"/>
+      <c r="A27" s="219"/>
+      <c r="E27" s="219"/>
+      <c r="G27" s="219"/>
+      <c r="I27" s="219"/>
       <c r="L27" s="71" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="221"/>
+      <c r="A28" s="219"/>
       <c r="D28" s="26"/>
-      <c r="E28" s="221"/>
-      <c r="G28" s="221"/>
-      <c r="I28" s="221"/>
+      <c r="E28" s="219"/>
+      <c r="G28" s="219"/>
+      <c r="I28" s="219"/>
       <c r="L28" s="71" t="s">
         <v>104</v>
       </c>

--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -1135,9 +1135,10 @@
 2023</t>
   </si>
   <si>
-    <t xml:space="preserve">MT1006 Differential Equations  BS(CE) -AB
+    <t xml:space="preserve">MT1006 Differential Equations  
+BS(CE) -AB
 BS(EE) -ABC, BS(CS) R
- 2025</t>
+2025</t>
   </si>
   <si>
     <t xml:space="preserve">EE3034 VLSI

--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -10,10 +10,10 @@
   <sheets>
     <sheet name="FSC" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="FSM" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="FSE" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="EE" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">FSE!$A$1:$L$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">EE!$A$1:$L$18</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">FSM!$A$1:$N$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,19 +26,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="270">
   <si>
     <t xml:space="preserve">National University of Computer &amp; Emerging Sciences, Islamabad Campus</t>
   </si>
   <si>
-    <t xml:space="preserve">Sessional-2 Exams Schedule  Spring - 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 to 13 April 2026    (FAST-School of Computing)        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final
-Issued: 03-April-26</t>
+    <t xml:space="preserve">Revised Sessional-2 Exams Schedule  Spring - 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 to 16 April 2026    (FAST-School of Computing)        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final-Revised
+Issued: 08-April-26</t>
   </si>
   <si>
     <t xml:space="preserve">Days &amp; Date</t>
@@ -114,9 +114,15 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">DS5007 Natural Language Processing MAI-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">CS4109 Big Data Analytics
 BS(CS) (A,B)
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS4002 Applied Programming MCS-1A</t>
   </si>
   <si>
     <t xml:space="preserve">AI4013 AI Product Development
@@ -138,6 +144,9 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">SE5004 Search-based Software Engineering MSE-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">CS3006 Parallel and Distributed Computing 
   BS(CY) (A,B)
  2022</t>
@@ -158,6 +167,9 @@
 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">CS5051 Malware Analysis and Detection MCY-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">CS3002 Information Security
 BS(CY) (A,B)
 2023</t>
@@ -166,6 +178,10 @@
     <t xml:space="preserve">SE4002 Fundamentals of Software Project Management
 BS(SE) (A,B)
 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS1022 Understanding of Holy Quran II
+MAI-2A MDS-2A PCS-2A </t>
   </si>
   <si>
     <t xml:space="preserve">SE3003 Web Engineering
@@ -184,9 +200,6 @@
     <t xml:space="preserve">CS3004 Software Design and Analysis             
 BS(CS) (A,B,C,D,E,F,G)
 2024      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumma Prayer</t>
   </si>
   <si>
     <t xml:space="preserve">MT1008  Multivariable Calculus 
@@ -211,6 +224,9 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">DS5004 Machine Learning for Data Science MDS-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI2002 Artificial Intelligence 
  BS(CS) (A,B,C,D,E,F,G) 
 BS(AI) (A,B,C)
@@ -223,6 +239,9 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">AI5003 Advanced Machine Learning MAI-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">SS2012 Technical and Business Writing
 BS(CY) (A,B)
 2024</t>
@@ -254,11 +273,17 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">CS5137 Deep Reinforcement Learning MAI-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">SE4011 Software Measurement and Metrics 
 BS(SE)-A,B,C,D,E,F, G
  2022</t>
   </si>
   <si>
+    <t xml:space="preserve">CS5006 Theory of Programming Languages MCS-1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AI3003 Artificial Neural Networks
 BS(AI) (A,B)
 2023</t>
@@ -285,12 +310,12 @@
   </si>
   <si>
     <t xml:space="preserve">EE3009 Computer Architecture
-BS(CS)(A,B,C,D,E,F,G)
+BS(CS) (A,B,C,D,E,F,G)
   2023</t>
   </si>
   <si>
     <t xml:space="preserve">MG4033 Digital Marketing
-BS(CS) (A,B,C,D
+BS(CS) (A,B,C,D)
 2022</t>
   </si>
   <si>
@@ -331,6 +356,12 @@
 2024 ( R )</t>
   </si>
   <si>
+    <t xml:space="preserve">AI5004 Advanced Topics in Generative AI MDS-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CY2004 Cyber Security MCY-1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">SE2004 Software Design and Architecture 
 BS(SE) (A,B,C) 
  2024</t>
@@ -343,13 +374,19 @@
 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">SS1021  Understanding of Holy Quran I
+PCS-1A 
+ Batch Spring 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">DS2003 Advanced Statistics 
 BS(DS) -A
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">CS1002  Programming Fundamentals  
-BS(CS) (A,B,C)      BS(SE) (A) 
+BS(CS) (A,B,C)      
+BS(SE) (A) 
 BS(AI) (A)
 BS(CY) (A)
 2025</t>
@@ -394,23 +431,42 @@
   </si>
   <si>
     <t xml:space="preserve">CS3009 Software Engineering
-BS(CS)(A,B,C,D,E,F,G)
+BS(CS) (A,B,C,D,E,F,G)
   2023</t>
   </si>
   <si>
     <t xml:space="preserve">CS3001 Computer Networks
  BS(CY)-(A,B) 
-2024</t>
+2024
+ MCY-1A</t>
   </si>
   <si>
     <t xml:space="preserve">DS3002 Data Mining 
-BS(DS)(A,B,C)
+BS(DS) (A,B,C)
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">DS5006 Deep Learning MAI-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">DS3005 Data Mining 
-BS(DS)(A,B,C)
+BS(DS) (A,B,C)
 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS5006 Deep Learning MDS-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI5009MLOps for Cloud-Native ApplicationsMDS-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE5006 Model Based Testing MSE-1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS5130 Securing the Internet of things MCY-1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS5027 Machine Learning MCS-1A</t>
   </si>
   <si>
     <t xml:space="preserve">CS1005 Discrete Structures 
@@ -457,6 +513,9 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">CS5037 Data Visualization MCS-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">CS4063 Natural Language Processing
 BS(DS)-A
 BS(SE)-A
@@ -468,6 +527,9 @@
  2022</t>
   </si>
   <si>
+    <t xml:space="preserve">CS5001 Research Methodology MCS-1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">CS4075 Cloud Computing
  BS(CS)-A,B
 BS(SE)-A,B,C
@@ -480,7 +542,7 @@
   </si>
   <si>
     <t xml:space="preserve">CS4031 Compiler Construction
-BS(CS)(A,B,C,D,E,F,G)
+BS(CS) (A,B,C,D,E,F,G)
 2023</t>
   </si>
   <si>
@@ -517,7 +579,7 @@
  2022</t>
   </si>
   <si>
-    <t xml:space="preserve">AI4002 Computer Vision
+    <t xml:space="preserve">AI4002Computer Vision
 BS(AI) (A,B)
 2023</t>
   </si>
@@ -566,10 +628,22 @@
  2022</t>
   </si>
   <si>
-    <t xml:space="preserve">CS3015 - Robotics Technology BS(CS)-A
+    <t xml:space="preserve">CS5020 Agentic AI MDS-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS2009 Design and Analysis of Algorithms MCS-1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS3015  Robotics Technology BS(CS)-A
  2022</t>
   </si>
   <si>
+    <t xml:space="preserve">CY5006 Advanced Network Security MCY-1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE5001 Advanced Software Requirement Engineering MSE-1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Detail seating plan will be shared separately on daily basis during examination and students should follow that seating plan accordingly</t>
   </si>
   <si>
@@ -579,10 +653,10 @@
     <t xml:space="preserve">Manager Academics</t>
   </si>
   <si>
-    <t xml:space="preserve">Sessional-2  Exams Schedule  Spring - 2026                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">09 to 13 April 2026                      FAST-School of Management               </t>
+    <t xml:space="preserve">Revised Sessional-2  Exams Schedule  Spring - 2026                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 to 16 April 2026                     FAST-School of Management               </t>
   </si>
   <si>
     <t xml:space="preserve">AF1002 Financial Accounting
@@ -620,6 +694,10 @@
 2024</t>
   </si>
   <si>
+    <t xml:space="preserve">MG5013 Finance for Managers 
+MB-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">BA4002 Predictive Analytics
 BS(BA)-8A,B
 2022</t>
@@ -643,6 +721,10 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">MG5024 Cases in Management
+ MB-2A                                                           </t>
+  </si>
+  <si>
     <t xml:space="preserve">AF3001 Financial Management
 BS(FT)-4A,B,C,D
 2024</t>
@@ -658,11 +740,38 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">BA5002 Data Driven Decision Making and Optimization
+MSBA-4A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AF3006 Financing New Ventures
 BS(FT)-8A
 2022</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MG6003 Research and Theory in Management
+PMG-2A
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2 Hours )</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">CS3010 Web Programming
 BS(FT)-6A,B
 2023</t>
@@ -671,6 +780,10 @@
     <t xml:space="preserve">MG3032 Project Management
 BBA-8A
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS1022 Understanding of Holy Quran II 
+ MSBA-2A PMG-2A</t>
   </si>
   <si>
     <t xml:space="preserve">MG1001Fundamentals of Management
@@ -707,6 +820,10 @@
 2024</t>
   </si>
   <si>
+    <t xml:space="preserve">MG4009 Managerial Economics
+MB-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AF3004 Accounting for Decision Making
 BS(AF)-6A,B
 2023</t>
@@ -720,6 +837,10 @@
     <t xml:space="preserve">MG4051 Supply Chain Operations
 BBA-8A
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA5003 Predictive Modelling
+MSBA-4A</t>
   </si>
   <si>
     <t xml:space="preserve">MG1002 Marketing Management
@@ -748,8 +869,34 @@
 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">AF5001 Applied Corporate Finance
+MB-2A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MG6016-Seminars in Management PMG-3A
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2 Hours )</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">BA2006 Fundamentals of Business Analytics
-BS(BA)-4A,B,C
+B(BA)-4A,B,C
 2024</t>
   </si>
   <si>
@@ -758,9 +905,34 @@
 2025</t>
   </si>
   <si>
+    <t xml:space="preserve">MG5063 Strategic Supply Chain Management
+MB-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">MG4013 Business Strategy
 BS(BA)-8A,B
 2022</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AF6001-Contemporary Trends in Finance PMG-1A  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2 Hours )</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">MG2011 Environmental Science and Sustainability for Business
@@ -772,6 +944,12 @@
     <t xml:space="preserve">SS2003 Psychology
 BBA-8A
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG5011 Advanced Research Methods
+MB-2A
+MSBA-2A
+</t>
   </si>
   <si>
     <t xml:space="preserve">MG2008 Data Analysis for Business I
@@ -809,6 +987,14 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">MG4002 Communication for Managers
+MB-4A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG5047 Decision Science for Business  
+MS(BA) 2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AF3002 Financial Statement Analysis
 BS(AF)-6A,B
 2023</t>
@@ -836,12 +1022,16 @@
 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">MG4012-Quantitative Methods  MB-2A      </t>
+  </si>
+  <si>
     <t xml:space="preserve">BA3005 Database Systems for Business
 BS(BA)-6A,B
 2023</t>
   </si>
   <si>
     <t xml:space="preserve">MG3033-Principles of Leadership
+2022
 BS(AF)-8A
 2022</t>
   </si>
@@ -867,12 +1057,11 @@
   </si>
   <si>
     <t xml:space="preserve">SS1006 English – II
- BS(AF)-2A,B
+BS(AF)-2A,B
 BBA-2A,B,C,D
 BS(FT)-2A,B,C,D
 BS(BA)-2A,B,C
-2025
-</t>
+2025</t>
   </si>
   <si>
     <t xml:space="preserve">MG4002 Communication for Managers
@@ -880,9 +1069,37 @@
 2022</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MG6004 Advanced Qualitative Research Methods
+PMG-2A
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2 Hours )</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">MG4063 Gen AI and Prompt Engineering for Business
 BS(BA)-8A
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS1021  Understanding of Holy Quran I
+PMG-1A 
+ Batch Spring 2026</t>
   </si>
   <si>
     <t xml:space="preserve">AF1001 Fundamentals of Accounting
@@ -920,6 +1137,10 @@
     <t xml:space="preserve">FT4002 AIand Growth Engineering in FinTech
 BS(FT)-8A
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG5012 Managing Human Resources
+MB-2A</t>
   </si>
   <si>
     <t xml:space="preserve">AF4018 Equity Analysis and Pricing
@@ -956,6 +1177,10 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">BA5004 Machine Learning Models for Business Analytics
+MSBA-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">AF4018 Equity Analysis and Pricing
 BS(AF)-8A
 2023</t>
@@ -971,6 +1196,10 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">MG5101 Financial Modeling and Simulation
+MB-2A</t>
+  </si>
+  <si>
     <t xml:space="preserve">FT4003 Data Driven Fintech
 BS(FT)-8A
 2022</t>
@@ -986,19 +1215,46 @@
 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">BA5011 Context-Driven Marketing and Product Analytics
+MSBA-4A</t>
+  </si>
+  <si>
     <t xml:space="preserve">MG4032 Advertising
 BBA-8A
 2022</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MG6002 Advanced Quantitative Research Methods
+PMG-2A
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (2 Hours )</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">.</t>
   </si>
   <si>
-    <t xml:space="preserve">09 to 13 April 2026                                       FAST-School of Engineering</t>
+    <t xml:space="preserve">13 to 16 April 2026                                    FAST-School of Engineering</t>
   </si>
   <si>
     <t xml:space="preserve">CS1011 Programming for Engineers
-BS(EE) -ABC
+BS(EE) -ABC 
 2025</t>
   </si>
   <si>
@@ -1018,7 +1274,9 @@
 2023</t>
   </si>
   <si>
-    <t xml:space="preserve">MT1001 Applied Calculus  BS(EE) 2025 R</t>
+    <t xml:space="preserve">MT1001 Applied Calculus  
+BS(EE) 
+2025</t>
   </si>
   <si>
     <t xml:space="preserve">CS2002 Data Structures and Algorithms
@@ -1026,7 +1284,7 @@
 2024</t>
   </si>
   <si>
-    <t xml:space="preserve">CS1002-Programming Fundamentals 
+    <t xml:space="preserve">CS1002 Programming Fundamentals 
 BS(CE) -AB
 2025</t>
   </si>
@@ -1046,9 +1304,14 @@
 2024</t>
   </si>
   <si>
+    <t xml:space="preserve">SS1022 Understanding of Holy Quran II 
+MEE-1A  PEE-1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">MT1004 Linear Algebra
-BS(EE) -ABC, BS(SE) A
- 2025</t>
+BS(EE) -ABC
+BS(SE)-A
+2025</t>
   </si>
   <si>
     <t xml:space="preserve">EE3031 Digital Signal Processing 
@@ -1072,9 +1335,9 @@
 2024</t>
   </si>
   <si>
-    <t xml:space="preserve">SS1022-Understanding of Holy Quran II
+    <t xml:space="preserve">SS1022 Understanding of Holy Quran II
 BS(CE) -AB
- 2025</t>
+2025</t>
   </si>
   <si>
     <t xml:space="preserve">EE3032 Power Electronics
@@ -1090,6 +1353,12 @@
     <t xml:space="preserve">IO3031 Introduction to Internet of Things
 BS(EE)-8A
 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EE5049 Computational Statistics MEE-1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EE6095 Stochastic ModelingPEE-1A</t>
   </si>
   <si>
     <t xml:space="preserve">MG3008 Engineering Economics
@@ -1130,6 +1399,12 @@
 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">EE 5006 Deep Learning MEE-1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EE 6005 Application of Deep Learning in Engineering PEE-1A</t>
+  </si>
+  <si>
     <t xml:space="preserve">EE3004 Feedback Control System
 BS(EE)-6A,B
 2023</t>
@@ -1137,7 +1412,8 @@
   <si>
     <t xml:space="preserve">MT1006 Differential Equations  
 BS(CE) -AB
-BS(EE) -ABC, BS(CS) R
+BS(EE) -ABC, 
+BS(CS) R
 2025</t>
   </si>
   <si>
@@ -1192,7 +1468,7 @@
     <numFmt numFmtId="166" formatCode="h:mm\ AM/PM"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd&quot;, &quot;mmmm\ dd&quot;, &quot;yyyy"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1330,6 +1606,13 @@
       <sz val="20"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1709,884 +1992,892 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="222">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3819,9 +4110,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="26" customFormat="true" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" s="26" customFormat="true" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>13</v>
@@ -3851,7 +4142,9 @@
         <v>19</v>
       </c>
       <c r="O5" s="24"/>
-      <c r="P5" s="25"/>
+      <c r="P5" s="25" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" s="26" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15"/>
@@ -3868,9 +4161,11 @@
       <c r="L6" s="18"/>
       <c r="M6" s="23"/>
       <c r="N6" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="P6" s="28"/>
+        <v>21</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" s="26" customFormat="true" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15"/>
@@ -3882,17 +4177,19 @@
       <c r="G7" s="20"/>
       <c r="I7" s="17"/>
       <c r="J7" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" s="30"/>
+        <v>25</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="8" s="26" customFormat="true" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15"/>
@@ -3901,7 +4198,7 @@
       <c r="D8" s="18"/>
       <c r="E8" s="17"/>
       <c r="F8" s="29" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G8" s="20"/>
       <c r="I8" s="17"/>
@@ -3909,7 +4206,7 @@
       <c r="L8" s="16"/>
       <c r="M8" s="23"/>
       <c r="N8" s="19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P8" s="31"/>
     </row>
@@ -3917,7 +4214,7 @@
       <c r="A9" s="15"/>
       <c r="C9" s="17"/>
       <c r="D9" s="27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" s="17"/>
       <c r="G9" s="20"/>
@@ -3925,17 +4222,19 @@
       <c r="J9" s="32"/>
       <c r="K9" s="22"/>
       <c r="L9" s="19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M9" s="23"/>
-      <c r="N9" s="33"/>
+      <c r="N9" s="33" t="s">
+        <v>31</v>
+      </c>
       <c r="P9" s="31"/>
     </row>
     <row r="10" s="26" customFormat="true" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15"/>
       <c r="C10" s="17"/>
       <c r="D10" s="19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" s="17"/>
       <c r="G10" s="20"/>
@@ -3956,7 +4255,7 @@
       <c r="I11" s="17"/>
       <c r="K11" s="22"/>
       <c r="L11" s="19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="31"/>
@@ -3971,7 +4270,9 @@
       <c r="I12" s="17"/>
       <c r="J12" s="32"/>
       <c r="K12" s="22"/>
-      <c r="L12" s="18"/>
+      <c r="L12" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="M12" s="23"/>
       <c r="N12" s="31"/>
       <c r="P12" s="31"/>
@@ -4009,37 +4310,37 @@
     </row>
     <row r="15" s="26" customFormat="true" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E15" s="20"/>
       <c r="F15" s="16" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G15" s="43"/>
-      <c r="H15" s="44" t="s">
-        <v>33</v>
-      </c>
+      <c r="H15" s="44"/>
       <c r="I15" s="43"/>
       <c r="J15" s="45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K15" s="46"/>
       <c r="L15" s="47" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M15" s="46"/>
       <c r="N15" s="27" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O15" s="24"/>
-      <c r="P15" s="48"/>
+      <c r="P15" s="48" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="16" s="26" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15"/>
@@ -4049,63 +4350,69 @@
       <c r="E16" s="20"/>
       <c r="F16" s="16"/>
       <c r="G16" s="49"/>
-      <c r="H16" s="44"/>
+      <c r="H16" s="50"/>
       <c r="I16" s="49"/>
       <c r="J16" s="45"/>
-      <c r="K16" s="50"/>
+      <c r="K16" s="51"/>
       <c r="L16" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="50"/>
+        <v>42</v>
+      </c>
+      <c r="M16" s="51"/>
       <c r="N16" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="P16" s="25"/>
+        <v>43</v>
+      </c>
+      <c r="P16" s="25" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="17" s="26" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15"/>
-      <c r="B17" s="51" t="s">
-        <v>39</v>
+      <c r="B17" s="52" t="s">
+        <v>45</v>
       </c>
       <c r="C17" s="20"/>
       <c r="E17" s="20"/>
       <c r="F17" s="16" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G17" s="49"/>
-      <c r="H17" s="44"/>
+      <c r="H17" s="50"/>
       <c r="I17" s="49"/>
       <c r="J17" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="50"/>
+        <v>47</v>
+      </c>
+      <c r="K17" s="51"/>
       <c r="L17" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="M17" s="50"/>
+        <v>48</v>
+      </c>
+      <c r="M17" s="51"/>
       <c r="N17" s="29" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P17" s="31"/>
     </row>
     <row r="18" s="26" customFormat="true" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15"/>
       <c r="B18" s="29" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C18" s="20"/>
       <c r="E18" s="20"/>
       <c r="F18" s="16"/>
       <c r="G18" s="49"/>
-      <c r="H18" s="44"/>
+      <c r="H18" s="50"/>
       <c r="I18" s="49"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="50"/>
+      <c r="J18" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="51"/>
       <c r="L18" s="27" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M18" s="49"/>
-      <c r="N18" s="28"/>
+      <c r="N18" s="28" t="s">
+        <v>53</v>
+      </c>
       <c r="P18" s="31"/>
     </row>
     <row r="19" s="26" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4114,36 +4421,36 @@
       <c r="C19" s="20"/>
       <c r="E19" s="20"/>
       <c r="F19" s="19" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G19" s="49"/>
-      <c r="H19" s="44"/>
+      <c r="H19" s="50"/>
       <c r="I19" s="49"/>
       <c r="J19" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" s="50"/>
+        <v>55</v>
+      </c>
+      <c r="K19" s="51"/>
       <c r="M19" s="49"/>
-      <c r="N19" s="52"/>
+      <c r="N19" s="53"/>
       <c r="P19" s="31"/>
     </row>
     <row r="20" s="26" customFormat="true" ht="80.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15"/>
       <c r="B20" s="19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="19" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E20" s="20"/>
       <c r="G20" s="49"/>
-      <c r="H20" s="44"/>
+      <c r="H20" s="50"/>
       <c r="I20" s="49"/>
       <c r="J20" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="50"/>
+        <v>58</v>
+      </c>
+      <c r="K20" s="51"/>
       <c r="M20" s="49"/>
       <c r="N20" s="31"/>
       <c r="P20" s="31"/>
@@ -4155,13 +4462,13 @@
       <c r="D21" s="36"/>
       <c r="E21" s="20"/>
       <c r="F21" s="37"/>
-      <c r="G21" s="53"/>
+      <c r="G21" s="54"/>
       <c r="H21" s="36"/>
-      <c r="I21" s="53"/>
+      <c r="I21" s="54"/>
       <c r="J21" s="27"/>
-      <c r="K21" s="54"/>
+      <c r="K21" s="55"/>
       <c r="L21" s="35"/>
-      <c r="M21" s="53"/>
+      <c r="M21" s="54"/>
       <c r="N21" s="37"/>
       <c r="O21" s="35"/>
       <c r="P21" s="37"/>
@@ -4186,37 +4493,39 @@
     </row>
     <row r="23" s="26" customFormat="true" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
-        <v>46123</v>
+        <v>46127</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="21" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E23" s="17"/>
       <c r="F23" s="27" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G23" s="43"/>
-      <c r="H23" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="55"/>
-      <c r="J23" s="56" t="s">
-        <v>55</v>
+      <c r="H23" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="57" t="s">
+        <v>63</v>
       </c>
       <c r="K23" s="46"/>
       <c r="L23" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="M23" s="57"/>
+        <v>64</v>
+      </c>
+      <c r="M23" s="58"/>
       <c r="N23" s="29" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="O23" s="24"/>
-      <c r="P23" s="58"/>
+      <c r="P23" s="59" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="24" s="26" customFormat="true" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15"/>
@@ -4226,122 +4535,130 @@
       <c r="E24" s="17"/>
       <c r="F24" s="27"/>
       <c r="G24" s="49"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="50"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="51"/>
       <c r="L24" s="27"/>
-      <c r="M24" s="60"/>
+      <c r="M24" s="61"/>
       <c r="N24" s="29"/>
-      <c r="P24" s="33"/>
-    </row>
-    <row r="25" s="26" customFormat="true" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P24" s="33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" s="26" customFormat="true" ht="90.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15"/>
       <c r="B25" s="16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
+      <c r="F25" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="G25" s="49"/>
       <c r="H25" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="K25" s="50"/>
+        <v>71</v>
+      </c>
+      <c r="I25" s="60"/>
+      <c r="J25" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="K25" s="51"/>
       <c r="L25" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="M25" s="60"/>
+        <v>73</v>
+      </c>
+      <c r="M25" s="61"/>
       <c r="N25" s="27" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="P25" s="31"/>
     </row>
     <row r="26" s="26" customFormat="true" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15"/>
       <c r="B26" s="27" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="18"/>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
       <c r="G26" s="49"/>
-      <c r="I26" s="59"/>
+      <c r="I26" s="60"/>
       <c r="J26" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="K26" s="50"/>
+        <v>76</v>
+      </c>
+      <c r="K26" s="51"/>
       <c r="L26" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="M26" s="60"/>
+        <v>77</v>
+      </c>
+      <c r="M26" s="61"/>
       <c r="N26" s="47" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="P26" s="31"/>
     </row>
     <row r="27" s="26" customFormat="true" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15"/>
       <c r="B27" s="29" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="31"/>
       <c r="E27" s="17"/>
       <c r="G27" s="49"/>
       <c r="H27" s="32"/>
-      <c r="I27" s="59"/>
+      <c r="I27" s="60"/>
       <c r="J27" s="31"/>
-      <c r="K27" s="50"/>
+      <c r="K27" s="51"/>
       <c r="L27" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="M27" s="60"/>
+        <v>80</v>
+      </c>
+      <c r="M27" s="61"/>
       <c r="N27" s="16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="P27" s="31"/>
     </row>
     <row r="28" s="26" customFormat="true" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15"/>
       <c r="B28" s="27" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="32"/>
       <c r="E28" s="17"/>
       <c r="G28" s="49"/>
       <c r="H28" s="32"/>
-      <c r="I28" s="59"/>
-      <c r="K28" s="50"/>
+      <c r="I28" s="60"/>
+      <c r="K28" s="51"/>
       <c r="L28" s="19"/>
-      <c r="M28" s="60"/>
-      <c r="N28" s="25"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="25" t="s">
+        <v>83</v>
+      </c>
       <c r="P28" s="31"/>
     </row>
     <row r="29" s="26" customFormat="true" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15"/>
       <c r="B29" s="19" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="32"/>
       <c r="E29" s="17"/>
       <c r="G29" s="49"/>
       <c r="H29" s="32"/>
-      <c r="I29" s="59"/>
+      <c r="I29" s="60"/>
       <c r="J29" s="31"/>
-      <c r="K29" s="50"/>
-      <c r="M29" s="60"/>
-      <c r="N29" s="58"/>
+      <c r="K29" s="51"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="59" t="s">
+        <v>85</v>
+      </c>
       <c r="P29" s="31"/>
     </row>
     <row r="30" s="26" customFormat="true" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4351,11 +4668,13 @@
       <c r="E30" s="17"/>
       <c r="G30" s="49"/>
       <c r="H30" s="32"/>
-      <c r="I30" s="59"/>
+      <c r="I30" s="60"/>
       <c r="J30" s="31"/>
-      <c r="K30" s="50"/>
-      <c r="M30" s="60"/>
-      <c r="N30" s="58"/>
+      <c r="K30" s="51"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="59" t="s">
+        <v>86</v>
+      </c>
       <c r="P30" s="31"/>
     </row>
     <row r="31" s="26" customFormat="true" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4365,11 +4684,13 @@
       <c r="E31" s="17"/>
       <c r="G31" s="49"/>
       <c r="H31" s="32"/>
-      <c r="I31" s="59"/>
+      <c r="I31" s="60"/>
       <c r="J31" s="31"/>
-      <c r="K31" s="50"/>
-      <c r="M31" s="60"/>
-      <c r="N31" s="30"/>
+      <c r="K31" s="51"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="30" t="s">
+        <v>87</v>
+      </c>
       <c r="P31" s="31"/>
     </row>
     <row r="32" s="26" customFormat="true" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4379,11 +4700,13 @@
       <c r="E32" s="17"/>
       <c r="G32" s="49"/>
       <c r="H32" s="32"/>
-      <c r="I32" s="59"/>
+      <c r="I32" s="60"/>
       <c r="J32" s="31"/>
-      <c r="K32" s="50"/>
-      <c r="M32" s="60"/>
-      <c r="N32" s="33"/>
+      <c r="K32" s="51"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="33" t="s">
+        <v>88</v>
+      </c>
       <c r="P32" s="31"/>
     </row>
     <row r="33" s="26" customFormat="true" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4393,142 +4716,148 @@
       <c r="D33" s="36"/>
       <c r="E33" s="17"/>
       <c r="F33" s="35"/>
-      <c r="G33" s="53"/>
+      <c r="G33" s="54"/>
       <c r="H33" s="36"/>
-      <c r="I33" s="62"/>
+      <c r="I33" s="63"/>
       <c r="J33" s="37"/>
-      <c r="K33" s="54"/>
+      <c r="K33" s="55"/>
       <c r="L33" s="35"/>
-      <c r="M33" s="63"/>
-      <c r="N33" s="28"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="28" t="s">
+        <v>89</v>
+      </c>
       <c r="O33" s="35"/>
       <c r="P33" s="37"/>
     </row>
     <row r="34" s="26" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="64"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
     </row>
     <row r="35" s="26" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="n">
-        <v>46125</v>
-      </c>
-      <c r="B35" s="56" t="s">
-        <v>73</v>
+        <v>46128</v>
+      </c>
+      <c r="B35" s="57" t="s">
+        <v>90</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="19" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E35" s="17"/>
-      <c r="F35" s="56" t="s">
-        <v>75</v>
+      <c r="F35" s="57" t="s">
+        <v>92</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="27" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="I35" s="17"/>
       <c r="J35" s="16" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="K35" s="20"/>
-      <c r="L35" s="56" t="s">
-        <v>78</v>
+      <c r="L35" s="57" t="s">
+        <v>95</v>
       </c>
       <c r="M35" s="17"/>
       <c r="N35" s="27" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="O35" s="24"/>
-      <c r="P35" s="28"/>
+      <c r="P35" s="28" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="36" s="26" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15"/>
-      <c r="B36" s="56"/>
+      <c r="B36" s="57"/>
       <c r="C36" s="17"/>
       <c r="D36" s="27" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E36" s="17"/>
-      <c r="F36" s="56"/>
+      <c r="F36" s="57"/>
       <c r="G36" s="20"/>
       <c r="H36" s="27" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="I36" s="17"/>
       <c r="J36" s="16"/>
       <c r="K36" s="20"/>
-      <c r="L36" s="56"/>
+      <c r="L36" s="57"/>
       <c r="M36" s="17"/>
       <c r="N36" s="27"/>
-      <c r="P36" s="28"/>
+      <c r="P36" s="28" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="37" s="26" customFormat="true" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15"/>
       <c r="B37" s="27" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="E37" s="17"/>
       <c r="F37" s="19" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="27" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="I37" s="17"/>
-      <c r="J37" s="51" t="s">
-        <v>86</v>
+      <c r="J37" s="52" t="s">
+        <v>105</v>
       </c>
       <c r="K37" s="20"/>
       <c r="L37" s="47" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="M37" s="17"/>
       <c r="N37" s="27" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="P37" s="31"/>
     </row>
     <row r="38" s="26" customFormat="true" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15"/>
       <c r="B38" s="16" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="19"/>
       <c r="G38" s="20"/>
       <c r="H38" s="27" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="I38" s="17"/>
       <c r="J38" s="19" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="K38" s="20"/>
       <c r="L38" s="19" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="M38" s="17"/>
       <c r="N38" s="21" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="P38" s="31"/>
     </row>
@@ -4538,23 +4867,23 @@
       <c r="C39" s="17"/>
       <c r="E39" s="17"/>
       <c r="F39" s="27" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G39" s="20"/>
-      <c r="H39" s="61" t="s">
-        <v>95</v>
+      <c r="H39" s="62" t="s">
+        <v>114</v>
       </c>
       <c r="I39" s="17"/>
-      <c r="J39" s="61" t="s">
-        <v>96</v>
+      <c r="J39" s="62" t="s">
+        <v>115</v>
       </c>
       <c r="K39" s="20"/>
       <c r="L39" s="19" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M39" s="17"/>
       <c r="N39" s="19" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="P39" s="31"/>
     </row>
@@ -4564,15 +4893,17 @@
       <c r="E40" s="17"/>
       <c r="G40" s="20"/>
       <c r="H40" s="16" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="I40" s="17"/>
       <c r="J40" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="K40" s="20"/>
       <c r="M40" s="17"/>
-      <c r="N40" s="58"/>
+      <c r="N40" s="59" t="s">
+        <v>120</v>
+      </c>
       <c r="P40" s="31"/>
     </row>
     <row r="41" s="26" customFormat="true" ht="62.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4580,103 +4911,109 @@
       <c r="C41" s="17"/>
       <c r="E41" s="17"/>
       <c r="G41" s="20"/>
-      <c r="H41" s="25"/>
+      <c r="H41" s="25" t="s">
+        <v>121</v>
+      </c>
       <c r="I41" s="17"/>
       <c r="J41" s="27" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="K41" s="20"/>
       <c r="M41" s="17"/>
-      <c r="N41" s="33"/>
+      <c r="N41" s="33" t="s">
+        <v>123</v>
+      </c>
       <c r="P41" s="31"/>
     </row>
     <row r="42" s="26" customFormat="true" ht="62.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15"/>
       <c r="B42" s="32"/>
       <c r="C42" s="17"/>
-      <c r="D42" s="65"/>
+      <c r="D42" s="66"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="65"/>
+      <c r="F42" s="66"/>
       <c r="G42" s="20"/>
-      <c r="H42" s="65"/>
+      <c r="H42" s="66"/>
       <c r="I42" s="17"/>
-      <c r="J42" s="65"/>
+      <c r="J42" s="66"/>
       <c r="K42" s="20"/>
-      <c r="L42" s="65"/>
+      <c r="L42" s="66"/>
       <c r="M42" s="17"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="65"/>
+      <c r="N42" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="O42" s="66"/>
       <c r="P42" s="32"/>
     </row>
     <row r="43" s="26" customFormat="true" ht="62.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15"/>
-      <c r="B43" s="66"/>
+      <c r="B43" s="67"/>
       <c r="C43" s="17"/>
-      <c r="D43" s="66"/>
+      <c r="D43" s="67"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="66"/>
+      <c r="F43" s="67"/>
       <c r="G43" s="20"/>
-      <c r="H43" s="66"/>
+      <c r="H43" s="67"/>
       <c r="I43" s="17"/>
-      <c r="J43" s="66"/>
+      <c r="J43" s="67"/>
       <c r="K43" s="20"/>
-      <c r="L43" s="66"/>
+      <c r="L43" s="67"/>
       <c r="M43" s="17"/>
-      <c r="N43" s="67"/>
-      <c r="O43" s="66"/>
+      <c r="N43" s="68"/>
+      <c r="O43" s="67"/>
       <c r="P43" s="36"/>
     </row>
     <row r="44" s="26" customFormat="true" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="68" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="68"/>
-      <c r="M44" s="68"/>
-      <c r="N44" s="68"/>
+      <c r="A44" s="69" t="s">
+        <v>125</v>
+      </c>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="69"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="69"/>
+      <c r="K44" s="69"/>
+      <c r="L44" s="69"/>
+      <c r="M44" s="69"/>
+      <c r="N44" s="69"/>
     </row>
     <row r="45" s="26" customFormat="true" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="69"/>
-      <c r="B45" s="69"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="70"/>
-      <c r="N45" s="71" t="s">
-        <v>103</v>
+      <c r="A45" s="70"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="71"/>
+      <c r="N45" s="72" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="46" s="26" customFormat="true" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="69"/>
-      <c r="B46" s="69"/>
-      <c r="C46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="I46" s="70"/>
-      <c r="N46" s="71" t="s">
-        <v>104</v>
+      <c r="A46" s="70"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="I46" s="71"/>
+      <c r="N46" s="72" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="47" s="26" customFormat="true" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="69"/>
-      <c r="B47" s="72"/>
-      <c r="F47" s="72"/>
-      <c r="J47" s="73"/>
+      <c r="A47" s="70"/>
+      <c r="B47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="J47" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="59">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:M3"/>
@@ -4703,7 +5040,6 @@
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E21"/>
     <mergeCell ref="F15:F16"/>
-    <mergeCell ref="H15:H20"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="J20:J21"/>
@@ -4966,7 +5302,7 @@
   <dimension ref="A1:P41"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="23.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="74" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="75" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="1.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.57"/>
@@ -4980,63 +5316,63 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="33.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="0.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="46.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="75" width="1.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="75" width="35.14"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="75" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="76" width="1.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="76" width="35.14"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="76" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" s="4" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="77" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="3" s="4" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="78" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="79"/>
+      <c r="A3" s="79" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="80"/>
       <c r="P3" s="7" t="s">
         <v>3</v>
       </c>
@@ -5078,267 +5414,289 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="80" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="84"/>
-      <c r="F5" s="85" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="84"/>
-      <c r="H5" s="81" t="s">
-        <v>110</v>
-      </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="K5" s="87"/>
-      <c r="L5" s="88" t="s">
-        <v>112</v>
-      </c>
-      <c r="M5" s="87"/>
-      <c r="N5" s="89"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="91"/>
+      <c r="A5" s="81" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="85"/>
+      <c r="F5" s="86" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="85"/>
+      <c r="H5" s="82" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="87"/>
+      <c r="J5" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="88"/>
+      <c r="L5" s="89" t="s">
+        <v>135</v>
+      </c>
+      <c r="M5" s="88"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="92" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="80"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="94" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="95"/>
-      <c r="J6" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="K6" s="92"/>
-      <c r="L6" s="85" t="s">
-        <v>116</v>
-      </c>
-      <c r="M6" s="96"/>
-      <c r="N6" s="97"/>
-      <c r="P6" s="91"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="86" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="94"/>
+      <c r="H6" s="95" t="s">
+        <v>138</v>
+      </c>
+      <c r="I6" s="96"/>
+      <c r="J6" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="93"/>
+      <c r="L6" s="86" t="s">
+        <v>140</v>
+      </c>
+      <c r="M6" s="97"/>
+      <c r="N6" s="98"/>
+      <c r="P6" s="92" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="80"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="88" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="93"/>
-      <c r="G7" s="93"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99" t="s">
-        <v>118</v>
-      </c>
-      <c r="K7" s="92"/>
-      <c r="L7" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="M7" s="96"/>
-      <c r="N7" s="100"/>
-      <c r="P7" s="101"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="100" t="s">
+        <v>143</v>
+      </c>
+      <c r="K7" s="93"/>
+      <c r="L7" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="M7" s="97"/>
+      <c r="N7" s="101"/>
+      <c r="P7" s="102" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="80"/>
-      <c r="B8" s="85" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="94" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="106"/>
-      <c r="J8" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="K8" s="102"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="107"/>
-      <c r="N8" s="108"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="110"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="86" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="103"/>
+      <c r="D8" s="104" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="105"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="95" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="107"/>
+      <c r="J8" s="86" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" s="103"/>
+      <c r="L8" s="82" t="s">
+        <v>150</v>
+      </c>
+      <c r="M8" s="108"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="111"/>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="111"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="113"/>
+      <c r="A9" s="112"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="113"/>
+      <c r="N9" s="114"/>
     </row>
     <row r="10" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="80" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B10" s="81" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="81" t="s">
-        <v>124</v>
-      </c>
-      <c r="E10" s="84"/>
-      <c r="F10" s="85" t="s">
-        <v>125</v>
-      </c>
-      <c r="G10" s="84"/>
-      <c r="H10" s="114" t="s">
-        <v>33</v>
-      </c>
+      <c r="A10" s="81" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="83"/>
+      <c r="D10" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="85"/>
+      <c r="F10" s="86" t="s">
+        <v>153</v>
+      </c>
+      <c r="G10" s="85"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="115"/>
       <c r="J10" s="116" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="K10" s="117"/>
-      <c r="L10" s="83" t="s">
-        <v>127</v>
-      </c>
-      <c r="M10" s="87"/>
-      <c r="N10" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="O10" s="90"/>
-      <c r="P10" s="91"/>
+      <c r="L10" s="84" t="s">
+        <v>155</v>
+      </c>
+      <c r="M10" s="88"/>
+      <c r="N10" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="O10" s="91"/>
+      <c r="P10" s="92" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="114"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="95" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="94"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="50"/>
       <c r="I11" s="118"/>
       <c r="J11" s="116" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="L11" s="119"/>
-      <c r="M11" s="96"/>
+      <c r="M11" s="97"/>
       <c r="N11" s="120" t="s">
-        <v>131</v>
-      </c>
-      <c r="P11" s="101"/>
+        <v>160</v>
+      </c>
+      <c r="P11" s="102" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="80"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="121" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="92"/>
-      <c r="D12" s="94" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="93"/>
+        <v>162</v>
+      </c>
+      <c r="C12" s="93"/>
+      <c r="D12" s="95" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="94"/>
       <c r="F12" s="120" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="93"/>
-      <c r="H12" s="114"/>
+        <v>164</v>
+      </c>
+      <c r="G12" s="94"/>
+      <c r="H12" s="50"/>
       <c r="I12" s="118"/>
       <c r="J12" s="116" t="s">
-        <v>135</v>
-      </c>
-      <c r="L12" s="100"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="P12" s="122"/>
+        <v>165</v>
+      </c>
+      <c r="L12" s="101"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="95" t="s">
+        <v>166</v>
+      </c>
+      <c r="P12" s="122" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="80"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="121"/>
-      <c r="C13" s="92"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="88" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="93"/>
-      <c r="H13" s="114"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="104" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="94"/>
+      <c r="F13" s="89" t="s">
+        <v>169</v>
+      </c>
+      <c r="G13" s="94"/>
+      <c r="H13" s="50"/>
       <c r="I13" s="118"/>
-      <c r="J13" s="81" t="s">
-        <v>138</v>
-      </c>
-      <c r="L13" s="100"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="101"/>
+      <c r="J13" s="82" t="s">
+        <v>170</v>
+      </c>
+      <c r="L13" s="101"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="102" t="s">
+        <v>171</v>
+      </c>
       <c r="P13" s="123"/>
     </row>
     <row r="14" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="80"/>
-      <c r="B14" s="85" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="102"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="88" t="s">
-        <v>140</v>
-      </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="K14" s="105"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="107"/>
-      <c r="N14" s="91"/>
-      <c r="O14" s="109"/>
-      <c r="P14" s="110"/>
+      <c r="A14" s="81"/>
+      <c r="B14" s="86" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="103"/>
+      <c r="D14" s="104" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="105"/>
+      <c r="F14" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="105"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="86" t="s">
+        <v>175</v>
+      </c>
+      <c r="K14" s="106"/>
+      <c r="L14" s="109"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="92" t="s">
+        <v>176</v>
+      </c>
+      <c r="O14" s="110"/>
+      <c r="P14" s="111"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="125"/>
-      <c r="B15" s="126"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="126"/>
-      <c r="M15" s="126"/>
-      <c r="N15" s="126"/>
-      <c r="O15" s="126"/>
-      <c r="P15" s="127"/>
+      <c r="A15" s="126"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="127"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="127"/>
+      <c r="P15" s="128"/>
     </row>
     <row r="16" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
@@ -5377,389 +5735,409 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="128" t="n">
-        <v>46123</v>
-      </c>
-      <c r="B17" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="85" t="s">
-        <v>143</v>
+      <c r="A17" s="129" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="86" t="s">
+        <v>178</v>
       </c>
       <c r="E17" s="115"/>
-      <c r="F17" s="129" t="s">
-        <v>144</v>
+      <c r="F17" s="130" t="s">
+        <v>179</v>
       </c>
       <c r="G17" s="115"/>
-      <c r="H17" s="85" t="s">
-        <v>145</v>
-      </c>
-      <c r="I17" s="86"/>
-      <c r="J17" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="K17" s="87"/>
-      <c r="L17" s="85" t="s">
-        <v>147</v>
-      </c>
-      <c r="M17" s="130"/>
-      <c r="N17" s="101"/>
-      <c r="O17" s="90"/>
-      <c r="P17" s="101"/>
+      <c r="H17" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" s="87"/>
+      <c r="J17" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="K17" s="88"/>
+      <c r="L17" s="86" t="s">
+        <v>182</v>
+      </c>
+      <c r="M17" s="131"/>
+      <c r="N17" s="102" t="s">
+        <v>183</v>
+      </c>
+      <c r="O17" s="91"/>
+      <c r="P17" s="102" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="128"/>
-      <c r="B18" s="81"/>
-      <c r="C18" s="92"/>
-      <c r="D18" s="94" t="s">
-        <v>148</v>
+      <c r="A18" s="129"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="95" t="s">
+        <v>185</v>
       </c>
       <c r="E18" s="118"/>
-      <c r="F18" s="94" t="s">
-        <v>149</v>
+      <c r="F18" s="95" t="s">
+        <v>186</v>
       </c>
       <c r="G18" s="118"/>
       <c r="H18" s="120" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="95"/>
-      <c r="J18" s="94" t="s">
-        <v>151</v>
-      </c>
-      <c r="K18" s="96"/>
-      <c r="L18" s="85"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="94" t="s">
-        <v>152</v>
-      </c>
-      <c r="P18" s="91"/>
+        <v>187</v>
+      </c>
+      <c r="I18" s="96"/>
+      <c r="J18" s="95" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" s="97"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="95" t="s">
+        <v>189</v>
+      </c>
+      <c r="P18" s="92" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="128"/>
-      <c r="B19" s="94" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="92"/>
-      <c r="D19" s="85" t="s">
-        <v>154</v>
+      <c r="A19" s="129"/>
+      <c r="B19" s="95" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="93"/>
+      <c r="D19" s="86" t="s">
+        <v>192</v>
       </c>
       <c r="E19" s="118"/>
-      <c r="F19" s="88" t="s">
-        <v>155</v>
+      <c r="F19" s="89" t="s">
+        <v>193</v>
       </c>
       <c r="G19" s="118"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="88" t="s">
-        <v>156</v>
-      </c>
-      <c r="K19" s="96"/>
-      <c r="L19" s="85" t="s">
-        <v>157</v>
-      </c>
-      <c r="M19" s="98"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="89" t="s">
+        <v>194</v>
+      </c>
+      <c r="K19" s="97"/>
+      <c r="L19" s="86" t="s">
+        <v>195</v>
+      </c>
+      <c r="M19" s="99"/>
       <c r="N19" s="119"/>
       <c r="P19" s="123"/>
     </row>
-    <row r="20" s="132" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="128"/>
-      <c r="B20" s="85" t="s">
-        <v>158</v>
-      </c>
-      <c r="C20" s="131"/>
-      <c r="D20" s="81" t="s">
-        <v>159</v>
+    <row r="20" s="133" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="129"/>
+      <c r="B20" s="86" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="132"/>
+      <c r="D20" s="82" t="s">
+        <v>197</v>
       </c>
       <c r="E20" s="118"/>
-      <c r="F20" s="85" t="s">
-        <v>160</v>
+      <c r="F20" s="86" t="s">
+        <v>198</v>
       </c>
       <c r="G20" s="118"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="103"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="104" t="s">
+        <v>199</v>
+      </c>
       <c r="K20" s="118"/>
       <c r="L20" s="120" t="s">
-        <v>161</v>
-      </c>
-      <c r="M20" s="98"/>
-      <c r="N20" s="100"/>
-      <c r="P20" s="133"/>
-    </row>
-    <row r="21" s="132" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="128"/>
-      <c r="C21" s="131"/>
-      <c r="D21" s="81"/>
+        <v>200</v>
+      </c>
+      <c r="M20" s="99"/>
+      <c r="N20" s="101"/>
+      <c r="P20" s="134"/>
+    </row>
+    <row r="21" s="133" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="129"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="82"/>
       <c r="E21" s="118"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="18" t="s">
+        <v>201</v>
+      </c>
       <c r="G21" s="118"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="134"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="135"/>
       <c r="K21" s="118"/>
-      <c r="M21" s="98"/>
-      <c r="N21" s="100"/>
-      <c r="P21" s="133"/>
-    </row>
-    <row r="22" s="132" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="128"/>
-      <c r="C22" s="131"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="101"/>
+      <c r="P21" s="134"/>
+    </row>
+    <row r="22" s="133" customFormat="true" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="129"/>
+      <c r="C22" s="132"/>
       <c r="E22" s="118"/>
       <c r="F22" s="18"/>
       <c r="G22" s="118"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="134"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="135"/>
       <c r="K22" s="118"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="100"/>
-      <c r="P22" s="133"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="101"/>
+      <c r="P22" s="134"/>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="135"/>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="137"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="138"/>
+      <c r="A23" s="136"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="137"/>
+      <c r="M23" s="137"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="139"/>
     </row>
     <row r="24" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="80" t="n">
-        <v>46125</v>
-      </c>
-      <c r="B24" s="81" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="87"/>
-      <c r="D24" s="88" t="s">
-        <v>163</v>
+      <c r="A24" s="81" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B24" s="82" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" s="88"/>
+      <c r="D24" s="89" t="s">
+        <v>203</v>
       </c>
       <c r="E24" s="115"/>
-      <c r="F24" s="94" t="s">
-        <v>164</v>
+      <c r="F24" s="95" t="s">
+        <v>204</v>
       </c>
       <c r="G24" s="115"/>
-      <c r="H24" s="88" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="139"/>
-      <c r="J24" s="81" t="s">
-        <v>166</v>
-      </c>
-      <c r="K24" s="87"/>
-      <c r="L24" s="81" t="s">
-        <v>167</v>
-      </c>
-      <c r="M24" s="130"/>
-      <c r="N24" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="O24" s="90"/>
-      <c r="P24" s="91"/>
+      <c r="H24" s="89" t="s">
+        <v>205</v>
+      </c>
+      <c r="I24" s="140"/>
+      <c r="J24" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="K24" s="88"/>
+      <c r="L24" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="M24" s="131"/>
+      <c r="N24" s="86" t="s">
+        <v>208</v>
+      </c>
+      <c r="O24" s="91"/>
+      <c r="P24" s="92" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="80"/>
+      <c r="A25" s="81"/>
       <c r="B25" s="120" t="s">
-        <v>169</v>
-      </c>
-      <c r="C25" s="140"/>
+        <v>210</v>
+      </c>
+      <c r="C25" s="141"/>
       <c r="D25" s="119"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="88" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25" s="124"/>
-      <c r="H25" s="120" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="124"/>
-      <c r="J25" s="85" t="s">
-        <v>172</v>
-      </c>
-      <c r="K25" s="124"/>
-      <c r="L25" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="M25" s="124"/>
-      <c r="N25" s="85" t="s">
-        <v>174</v>
-      </c>
-      <c r="P25" s="101"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="89" t="s">
+        <v>211</v>
+      </c>
+      <c r="G25" s="125"/>
+      <c r="H25" s="142" t="s">
+        <v>212</v>
+      </c>
+      <c r="I25" s="125"/>
+      <c r="J25" s="86" t="s">
+        <v>213</v>
+      </c>
+      <c r="K25" s="125"/>
+      <c r="L25" s="89" t="s">
+        <v>214</v>
+      </c>
+      <c r="M25" s="125"/>
+      <c r="N25" s="86" t="s">
+        <v>215</v>
+      </c>
+      <c r="P25" s="102" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="102.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="80"/>
-      <c r="B26" s="85" t="s">
-        <v>175</v>
-      </c>
-      <c r="C26" s="140"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="124"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="94" t="s">
-        <v>176</v>
-      </c>
-      <c r="K26" s="124"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="124"/>
-      <c r="N26" s="85" t="s">
-        <v>177</v>
-      </c>
-      <c r="P26" s="101"/>
-    </row>
-    <row r="27" s="132" customFormat="true" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="80"/>
-      <c r="B27" s="85" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" s="140"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="142"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="143" t="s">
-        <v>179</v>
-      </c>
-      <c r="K27" s="124"/>
-      <c r="L27" s="94" t="s">
-        <v>180</v>
-      </c>
-      <c r="M27" s="124"/>
-      <c r="N27" s="101"/>
-      <c r="P27" s="133"/>
-    </row>
-    <row r="28" s="132" customFormat="true" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="80"/>
-      <c r="B28" s="85" t="s">
-        <v>181</v>
-      </c>
-      <c r="C28" s="140"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="144"/>
-      <c r="I28" s="124"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="145"/>
-      <c r="M28" s="124"/>
-      <c r="N28" s="146"/>
-      <c r="O28" s="145"/>
-      <c r="P28" s="146"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="86" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="141"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="125"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="125"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="95" t="s">
+        <v>218</v>
+      </c>
+      <c r="K26" s="125"/>
+      <c r="L26" s="89"/>
+      <c r="M26" s="125"/>
+      <c r="N26" s="86" t="s">
+        <v>219</v>
+      </c>
+      <c r="P26" s="102" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" s="133" customFormat="true" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="81"/>
+      <c r="B27" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="C27" s="141"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="144"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="145" t="s">
+        <v>222</v>
+      </c>
+      <c r="K27" s="125"/>
+      <c r="L27" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="M27" s="125"/>
+      <c r="N27" s="102" t="s">
+        <v>224</v>
+      </c>
+      <c r="P27" s="134"/>
+    </row>
+    <row r="28" s="133" customFormat="true" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="81"/>
+      <c r="B28" s="86" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="141"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="146"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="104" t="s">
+        <v>226</v>
+      </c>
+      <c r="K28" s="125"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="125"/>
+      <c r="N28" s="148"/>
+      <c r="O28" s="147"/>
+      <c r="P28" s="148"/>
     </row>
     <row r="29" s="26" customFormat="true" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="147" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="147"/>
-      <c r="C29" s="147"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="147"/>
-      <c r="G29" s="147"/>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="147"/>
-      <c r="K29" s="147"/>
-      <c r="L29" s="147"/>
-      <c r="M29" s="147"/>
-      <c r="N29" s="147"/>
+      <c r="A29" s="149" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="149"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="149"/>
+      <c r="G29" s="149"/>
+      <c r="H29" s="149"/>
+      <c r="I29" s="149"/>
+      <c r="J29" s="149"/>
+      <c r="K29" s="149"/>
+      <c r="L29" s="149"/>
+      <c r="M29" s="149"/>
+      <c r="N29" s="149"/>
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="148"/>
-      <c r="B30" s="148"/>
-      <c r="C30" s="148"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
-      <c r="H30" s="148"/>
-      <c r="I30" s="148"/>
-      <c r="J30" s="148"/>
-      <c r="K30" s="148"/>
-      <c r="L30" s="148"/>
-      <c r="M30" s="148"/>
-      <c r="N30" s="148"/>
+      <c r="A30" s="150"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="150"/>
+      <c r="E30" s="150"/>
+      <c r="F30" s="150"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="150"/>
+      <c r="N30" s="150"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="149"/>
-      <c r="B31" s="150"/>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="148"/>
-      <c r="K31" s="148"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" s="75" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="151"/>
-      <c r="B32" s="150"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="154" t="s">
-        <v>182</v>
-      </c>
-      <c r="I32" s="154"/>
-      <c r="J32" s="154"/>
-      <c r="K32" s="154"/>
-      <c r="L32" s="155"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="155" t="s">
-        <v>104</v>
+      <c r="A31" s="151"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="150"/>
+      <c r="D31" s="150"/>
+      <c r="E31" s="150"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="72" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" s="76" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="153"/>
+      <c r="B32" s="152"/>
+      <c r="C32" s="154"/>
+      <c r="D32" s="154"/>
+      <c r="E32" s="154"/>
+      <c r="G32" s="155"/>
+      <c r="H32" s="156" t="s">
+        <v>227</v>
+      </c>
+      <c r="I32" s="156"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="156"/>
+      <c r="L32" s="157"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="157" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G33" s="153"/>
+      <c r="G33" s="155"/>
       <c r="H33" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="I33" s="154"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="154"/>
-      <c r="N33" s="154"/>
-    </row>
-    <row r="35" s="75" customFormat="true" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="73"/>
-    </row>
-    <row r="36" s="75" customFormat="true" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D36" s="73"/>
-    </row>
-    <row r="39" s="75" customFormat="true" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>227</v>
+      </c>
+      <c r="I33" s="156"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="156"/>
+    </row>
+    <row r="35" s="76" customFormat="true" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="74"/>
+    </row>
+    <row r="36" s="76" customFormat="true" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D36" s="74"/>
+    </row>
+    <row r="39" s="76" customFormat="true" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D39" s="1"/>
     </row>
-    <row r="40" s="75" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" s="76" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D40" s="1"/>
     </row>
-    <row r="41" s="75" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" s="76" customFormat="true" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D41" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:L3"/>
@@ -5770,7 +6148,6 @@
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H10:H14"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="B17:B18"/>
@@ -5808,71 +6185,71 @@
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="72" width="55.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="72" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="72" width="50.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="73" width="55.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="73" width="3.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="73" width="50.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="2.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="26" width="54.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="26" width="2.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="26" width="54.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="26" width="2.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="72" width="51.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="72" width="2.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="72" width="51.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="73" width="51.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="73" width="2.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="73" width="51.15"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="26" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="158" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
     </row>
     <row r="2" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="159" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
     </row>
     <row r="3" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="158" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="159"/>
+      <c r="A3" s="160" t="s">
+        <v>228</v>
+      </c>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="161"/>
       <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="160" customFormat="true" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" s="162" customFormat="true" ht="73.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
@@ -5900,411 +6277,419 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" s="74" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="n">
-        <v>46121</v>
-      </c>
-      <c r="B5" s="161" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="162"/>
-      <c r="D5" s="163" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="164"/>
-      <c r="F5" s="165" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="166"/>
-      <c r="H5" s="167" t="s">
-        <v>187</v>
-      </c>
-      <c r="I5" s="168"/>
-      <c r="J5" s="169" t="s">
-        <v>188</v>
-      </c>
-      <c r="K5" s="170"/>
-      <c r="L5" s="171" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="163" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="164"/>
+      <c r="D5" s="165" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="166"/>
+      <c r="F5" s="167" t="s">
+        <v>231</v>
+      </c>
+      <c r="G5" s="168"/>
+      <c r="H5" s="169" t="s">
+        <v>232</v>
+      </c>
+      <c r="I5" s="170"/>
+      <c r="J5" s="171" t="s">
+        <v>233</v>
+      </c>
+      <c r="K5" s="172"/>
+      <c r="L5" s="173" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" s="74" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15"/>
-      <c r="B6" s="172" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="173"/>
-      <c r="D6" s="163"/>
-      <c r="E6" s="174"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="177"/>
-      <c r="K6" s="178"/>
-      <c r="L6" s="179" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="174" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="175"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="180"/>
+      <c r="L6" s="181" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" s="74" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15"/>
-      <c r="B7" s="172"/>
-      <c r="C7" s="180"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="174"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="182"/>
-      <c r="K7" s="178"/>
-      <c r="L7" s="183" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" s="73" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="174"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="183"/>
+      <c r="E7" s="176"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="178"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="184"/>
+      <c r="K7" s="180"/>
+      <c r="L7" s="185" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" s="74" customFormat="true" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15"/>
-      <c r="B8" s="169" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="184"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="187"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="189"/>
-      <c r="J8" s="190"/>
-      <c r="K8" s="191"/>
-      <c r="L8" s="172"/>
-    </row>
-    <row r="9" s="73" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="192"/>
-      <c r="B9" s="193"/>
-      <c r="C9" s="193"/>
-      <c r="D9" s="193"/>
-      <c r="E9" s="193"/>
-      <c r="F9" s="193"/>
-      <c r="G9" s="193"/>
-      <c r="H9" s="193"/>
-      <c r="I9" s="193"/>
-      <c r="J9" s="193"/>
-      <c r="K9" s="193"/>
-      <c r="L9" s="194"/>
-    </row>
-    <row r="10" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="171" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="186"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="188"/>
+      <c r="F8" s="189"/>
+      <c r="G8" s="190"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
+      <c r="J8" s="192"/>
+      <c r="K8" s="193"/>
+      <c r="L8" s="174" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" s="74" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="194"/>
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
+      <c r="D9" s="195"/>
+      <c r="E9" s="195"/>
+      <c r="F9" s="195"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="195"/>
+      <c r="I9" s="195"/>
+      <c r="J9" s="195"/>
+      <c r="K9" s="195"/>
+      <c r="L9" s="196"/>
+    </row>
+    <row r="10" s="74" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B10" s="161" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="195"/>
-      <c r="D10" s="196" t="s">
-        <v>195</v>
-      </c>
-      <c r="E10" s="164"/>
-      <c r="F10" s="172" t="s">
-        <v>196</v>
-      </c>
-      <c r="G10" s="164"/>
-      <c r="H10" s="114" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="168"/>
-      <c r="J10" s="197" t="s">
-        <v>197</v>
-      </c>
-      <c r="K10" s="198"/>
-      <c r="L10" s="171" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46126</v>
+      </c>
+      <c r="B10" s="163" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="197"/>
+      <c r="D10" s="198" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" s="166"/>
+      <c r="F10" s="174" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" s="166"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="170"/>
+      <c r="J10" s="199" t="s">
+        <v>243</v>
+      </c>
+      <c r="K10" s="200"/>
+      <c r="L10" s="173" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" s="74" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15"/>
-      <c r="B11" s="161" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" s="199"/>
-      <c r="D11" s="196"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="172"/>
-      <c r="G11" s="174"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="197" t="s">
-        <v>200</v>
-      </c>
-      <c r="K11" s="200"/>
-      <c r="L11" s="165" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="12" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="163" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="201"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="174"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="178"/>
+      <c r="J11" s="199" t="s">
+        <v>246</v>
+      </c>
+      <c r="K11" s="202"/>
+      <c r="L11" s="167" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" s="74" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15"/>
-      <c r="B12" s="179" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="199"/>
-      <c r="D12" s="168"/>
-      <c r="E12" s="174"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="174"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="177"/>
-      <c r="K12" s="200"/>
-      <c r="L12" s="201"/>
-    </row>
-    <row r="13" s="73" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="181" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="201"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="178"/>
+      <c r="J12" s="179"/>
+      <c r="K12" s="202"/>
+      <c r="L12" s="203" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" s="74" customFormat="true" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15"/>
-      <c r="B13" s="202"/>
-      <c r="C13" s="199"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="174"/>
-      <c r="F13" s="190"/>
-      <c r="G13" s="174"/>
-      <c r="H13" s="114"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="190"/>
-      <c r="K13" s="203"/>
-      <c r="L13" s="201"/>
-    </row>
-    <row r="14" s="73" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="204"/>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
-      <c r="F14" s="205"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="205"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="206"/>
-    </row>
-    <row r="15" s="73" customFormat="true" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="204"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="191"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="192"/>
+      <c r="G13" s="176"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="178"/>
+      <c r="J13" s="192"/>
+      <c r="K13" s="205"/>
+      <c r="L13" s="203" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" s="74" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="206"/>
+      <c r="B14" s="207"/>
+      <c r="C14" s="207"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+      <c r="F14" s="207"/>
+      <c r="G14" s="207"/>
+      <c r="H14" s="207"/>
+      <c r="I14" s="207"/>
+      <c r="J14" s="207"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="208"/>
+    </row>
+    <row r="15" s="74" customFormat="true" ht="133.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
-        <v>46123</v>
-      </c>
-      <c r="B15" s="207" t="s">
-        <v>203</v>
-      </c>
-      <c r="C15" s="208"/>
-      <c r="D15" s="172" t="s">
-        <v>204</v>
-      </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="209" t="s">
-        <v>205</v>
-      </c>
-      <c r="G15" s="166"/>
-      <c r="H15" s="197" t="s">
-        <v>206</v>
-      </c>
-      <c r="I15" s="168"/>
-      <c r="J15" s="169" t="s">
-        <v>207</v>
-      </c>
-      <c r="K15" s="168"/>
-      <c r="L15" s="171" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" s="73" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46127</v>
+      </c>
+      <c r="B15" s="209" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="210"/>
+      <c r="D15" s="174" t="s">
+        <v>252</v>
+      </c>
+      <c r="E15" s="166"/>
+      <c r="F15" s="211" t="s">
+        <v>253</v>
+      </c>
+      <c r="G15" s="168"/>
+      <c r="H15" s="199" t="s">
+        <v>254</v>
+      </c>
+      <c r="I15" s="170"/>
+      <c r="J15" s="171" t="s">
+        <v>255</v>
+      </c>
+      <c r="K15" s="170"/>
+      <c r="L15" s="173" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="16" s="74" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15"/>
-      <c r="B16" s="207"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="172"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="209"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="197"/>
-      <c r="I16" s="176"/>
-      <c r="K16" s="176"/>
-      <c r="L16" s="210" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="17" s="73" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="209"/>
+      <c r="C16" s="205"/>
+      <c r="D16" s="174"/>
+      <c r="E16" s="176"/>
+      <c r="F16" s="211"/>
+      <c r="G16" s="177"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="178"/>
+      <c r="K16" s="178"/>
+      <c r="L16" s="212" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="17" s="74" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15"/>
-      <c r="B17" s="168"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="175"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="176"/>
-      <c r="K17" s="176"/>
-      <c r="L17" s="201"/>
-    </row>
-    <row r="18" s="73" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="170"/>
+      <c r="C17" s="205"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="176"/>
+      <c r="F17" s="170"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="179"/>
+      <c r="I17" s="178"/>
+      <c r="K17" s="178"/>
+      <c r="L17" s="203" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" s="74" customFormat="true" ht="110.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15"/>
-      <c r="B18" s="189"/>
-      <c r="C18" s="211"/>
-      <c r="D18" s="190"/>
-      <c r="E18" s="174"/>
-      <c r="F18" s="189"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="190"/>
-      <c r="I18" s="176"/>
-      <c r="K18" s="176"/>
-      <c r="L18" s="201"/>
-    </row>
-    <row r="19" s="73" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="204"/>
-      <c r="B19" s="205"/>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="205"/>
-      <c r="F19" s="205"/>
-      <c r="G19" s="205"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="205"/>
-      <c r="K19" s="205"/>
-      <c r="L19" s="206"/>
-    </row>
-    <row r="20" s="73" customFormat="true" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="191"/>
+      <c r="C18" s="213"/>
+      <c r="D18" s="192"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="191"/>
+      <c r="G18" s="177"/>
+      <c r="H18" s="192"/>
+      <c r="I18" s="178"/>
+      <c r="K18" s="178"/>
+      <c r="L18" s="203" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" s="74" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="206"/>
+      <c r="B19" s="207"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="207"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="207"/>
+      <c r="G19" s="207"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="207"/>
+      <c r="J19" s="207"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="208"/>
+    </row>
+    <row r="20" s="74" customFormat="true" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
-        <v>46125</v>
-      </c>
-      <c r="B20" s="207" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="162"/>
-      <c r="D20" s="172" t="s">
-        <v>211</v>
-      </c>
-      <c r="E20" s="164"/>
-      <c r="F20" s="179" t="s">
-        <v>212</v>
-      </c>
-      <c r="G20" s="166"/>
-      <c r="H20" s="209" t="s">
-        <v>213</v>
-      </c>
-      <c r="I20" s="168"/>
-      <c r="J20" s="177"/>
-      <c r="K20" s="168"/>
-      <c r="L20" s="165" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" s="73" customFormat="true" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>46128</v>
+      </c>
+      <c r="B20" s="209" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="164"/>
+      <c r="D20" s="174" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" s="166"/>
+      <c r="F20" s="181" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="168"/>
+      <c r="H20" s="211" t="s">
+        <v>263</v>
+      </c>
+      <c r="I20" s="170"/>
+      <c r="J20" s="179"/>
+      <c r="K20" s="170"/>
+      <c r="L20" s="167" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" s="74" customFormat="true" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15"/>
-      <c r="B21" s="207"/>
-      <c r="C21" s="212"/>
-      <c r="D21" s="172"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="179" t="s">
-        <v>215</v>
-      </c>
-      <c r="G21" s="175"/>
-      <c r="H21" s="209"/>
-      <c r="I21" s="176"/>
-      <c r="J21" s="182"/>
-      <c r="K21" s="176"/>
-      <c r="L21" s="163" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" s="73" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="209"/>
+      <c r="C21" s="214"/>
+      <c r="D21" s="174"/>
+      <c r="E21" s="176"/>
+      <c r="F21" s="181" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" s="177"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="178"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="178"/>
+      <c r="L21" s="165" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" s="74" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15"/>
-      <c r="B22" s="165" t="s">
-        <v>217</v>
-      </c>
-      <c r="C22" s="162"/>
-      <c r="D22" s="213" t="s">
-        <v>218</v>
-      </c>
-      <c r="E22" s="174"/>
-      <c r="F22" s="214"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="182"/>
-      <c r="K22" s="176"/>
-      <c r="L22" s="169" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="23" s="73" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="167" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="164"/>
+      <c r="D22" s="215" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22" s="176"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="178"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="178"/>
+      <c r="L22" s="171" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" s="74" customFormat="true" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15"/>
-      <c r="B23" s="215"/>
-      <c r="D23" s="189"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="202"/>
-      <c r="G23" s="188"/>
-      <c r="H23" s="202"/>
-      <c r="I23" s="189"/>
-      <c r="J23" s="216"/>
-      <c r="K23" s="189"/>
-      <c r="L23" s="190"/>
+      <c r="B23" s="217"/>
+      <c r="D23" s="191"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="204"/>
+      <c r="G23" s="190"/>
+      <c r="H23" s="204"/>
+      <c r="I23" s="191"/>
+      <c r="J23" s="218"/>
+      <c r="K23" s="191"/>
+      <c r="L23" s="192"/>
     </row>
     <row r="24" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="217" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="217"/>
-      <c r="C24" s="217"/>
-      <c r="D24" s="217"/>
-      <c r="E24" s="217"/>
-      <c r="F24" s="217"/>
-      <c r="G24" s="217"/>
-      <c r="H24" s="217"/>
-      <c r="I24" s="217"/>
-      <c r="J24" s="217"/>
-      <c r="K24" s="217"/>
-      <c r="L24" s="217"/>
+      <c r="A24" s="219" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="219"/>
+      <c r="C24" s="219"/>
+      <c r="D24" s="219"/>
+      <c r="E24" s="219"/>
+      <c r="F24" s="219"/>
+      <c r="G24" s="219"/>
+      <c r="H24" s="219"/>
+      <c r="I24" s="219"/>
+      <c r="J24" s="219"/>
+      <c r="K24" s="219"/>
+      <c r="L24" s="219"/>
     </row>
     <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="218"/>
-      <c r="B25" s="218"/>
-      <c r="C25" s="218"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="G25" s="218"/>
-      <c r="H25" s="218"/>
-      <c r="I25" s="218"/>
-      <c r="J25" s="218"/>
-      <c r="K25" s="218"/>
-      <c r="L25" s="218"/>
+      <c r="A25" s="220"/>
+      <c r="B25" s="220"/>
+      <c r="C25" s="220"/>
+      <c r="D25" s="220"/>
+      <c r="E25" s="220"/>
+      <c r="G25" s="220"/>
+      <c r="H25" s="220"/>
+      <c r="I25" s="220"/>
+      <c r="J25" s="220"/>
+      <c r="K25" s="220"/>
+      <c r="L25" s="220"/>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="218"/>
-      <c r="E26" s="218"/>
-      <c r="F26" s="218"/>
-      <c r="G26" s="218"/>
-      <c r="H26" s="218"/>
-      <c r="I26" s="218"/>
-      <c r="J26" s="218"/>
-      <c r="K26" s="218"/>
-      <c r="L26" s="218"/>
+      <c r="A26" s="220"/>
+      <c r="E26" s="220"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="220"/>
+      <c r="H26" s="220"/>
+      <c r="I26" s="220"/>
+      <c r="J26" s="220"/>
+      <c r="K26" s="220"/>
+      <c r="L26" s="220"/>
     </row>
     <row r="27" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="219"/>
-      <c r="E27" s="219"/>
-      <c r="G27" s="219"/>
-      <c r="I27" s="219"/>
-      <c r="L27" s="71" t="s">
-        <v>103</v>
+      <c r="A27" s="221"/>
+      <c r="E27" s="221"/>
+      <c r="G27" s="221"/>
+      <c r="I27" s="221"/>
+      <c r="L27" s="72" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="219"/>
+      <c r="A28" s="221"/>
       <c r="D28" s="26"/>
-      <c r="E28" s="219"/>
-      <c r="G28" s="219"/>
-      <c r="I28" s="219"/>
-      <c r="L28" s="71" t="s">
-        <v>104</v>
+      <c r="E28" s="221"/>
+      <c r="G28" s="221"/>
+      <c r="I28" s="221"/>
+      <c r="L28" s="72" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:J3"/>
@@ -6315,7 +6700,6 @@
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="H10:H13"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="D15:D16"/>

--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="FSC" sheetId="1" state="visible" r:id="rId3"/>
@@ -579,7 +579,7 @@
  2022</t>
   </si>
   <si>
-    <t xml:space="preserve">AI4002Computer Vision
+    <t xml:space="preserve">AI4002 Computer Vision
 BS(AI) (A,B)
 2023</t>
   </si>
@@ -603,7 +603,7 @@
  2022</t>
   </si>
   <si>
-    <t xml:space="preserve">AI4002Computer Vision
+    <t xml:space="preserve">AI4002 Computer Vision
 BS(AI) (A)
 2022</t>
   </si>
@@ -1997,887 +1997,887 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="18" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="45" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="19" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="23" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/exam_schedule.xlsx
+++ b/exam_schedule.xlsx
@@ -77,7 +77,8 @@
   </si>
   <si>
     <t xml:space="preserve">SS1014  Expository Writing
-  BS(CS) (A,B,C,D,E,F, G,H, J)      BS(SE) (A,B,C,D) 
+BS(CS) (A,B,C,D,E,F, G,H, J)      
+BS(SE) (A,B,C,D) 
 BS(AI) (A,B, C)
 BS(DS) (A,B)
 BS(CY) (A,B,C)
@@ -203,7 +204,8 @@
   </si>
   <si>
     <t xml:space="preserve">MT1008  Multivariable Calculus 
-  BS(CS) (A,B,C,D,E,F, G,H, J)      BS(SE) (A,B,C,D) 
+BS(CS) (A,B,C,D,E,F, G,H, J)      
+BS(SE) (A,B,C,D) 
 BS(AI) (A,B, C)
 BS(DS) (A,B)
 BS(CY) (A,B,C)
@@ -335,7 +337,8 @@
   </si>
   <si>
     <t xml:space="preserve">CS1004 Object Oriented Programming   
- BS(CS) (A,B,C,D,E,F, G,H, J)      BS(SE) (A,B,C,D) 
+BS(CS) (A,B,C,D,E,F, G,H, J)      
+BS(SE) (A,B,C,D) 
 BS(AI) (A,B, C)
 BS(DS) (A,B)
 BS(CY) (A,B,C)
